--- a/Template/Voucher Template.xlsx
+++ b/Template/Voucher Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Smart Travel PC\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{674D8F4C-64AA-4864-BFCA-31888FEE4F0F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71E23664-119A-47C9-88C0-F339A9350669}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12690" yWindow="45" windowWidth="16065" windowHeight="15705" xr2:uid="{46FCF62E-0F38-40EF-B40B-6239A54C7BFA}"/>
+    <workbookView xWindow="1170" yWindow="45" windowWidth="10860" windowHeight="15705" xr2:uid="{46FCF62E-0F38-40EF-B40B-6239A54C7BFA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="48">
   <si>
     <t>TO:</t>
   </si>
@@ -112,9 +112,6 @@
   </si>
   <si>
     <t>Meals (4 times Lunch, 4 times Dinner)</t>
-  </si>
-  <si>
-    <t>(Coach,Van), Admission as the itinerary, ENGLISH guide etc.</t>
   </si>
   <si>
     <t>*** It will be subject to change as the local situation ***</t>
@@ -178,19 +175,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFFF0000"/>
-      <name val="Bahnschrift"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -218,21 +209,7 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
-      <color theme="1"/>
-      <name val="Bahnschrift"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Bahnschrift"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
       <color theme="1"/>
       <name val="Bahnschrift"/>
       <family val="2"/>
@@ -245,33 +222,19 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="8"/>
       <color theme="1"/>
       <name val="Bahnschrift"/>
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <name val="Bahnschrift"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="8.5"/>
-      <color theme="1"/>
-      <name val="Bahnschrift"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
+      <sz val="10"/>
       <color rgb="FFFF0000"/>
-      <name val="Bahnschrift"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color theme="1"/>
       <name val="Bahnschrift"/>
       <family val="2"/>
     </font>
@@ -477,308 +440,272 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="14" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1148,7 +1075,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E608D469-AF7C-422E-92CF-2B4802A6A2AF}">
-  <dimension ref="A1:N46"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="8" style="3" customWidth="1"/>
@@ -1176,115 +1103,115 @@
       <c r="K1" s="2"/>
     </row>
     <row r="2" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="101" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" s="102"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="103" t="s">
+      <c r="A2" s="76" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="77"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="44"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="46"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="68"/>
       <c r="N2" s="2"/>
     </row>
     <row r="3" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="49"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="70"/>
       <c r="N3" s="2"/>
     </row>
     <row r="4" spans="1:14" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="8"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="11"/>
+      <c r="A4" s="16"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="9"/>
       <c r="N4" s="2"/>
     </row>
     <row r="5" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="53" t="s">
+      <c r="B5" s="72" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="74" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="75"/>
+      <c r="H5" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="71"/>
+      <c r="J5" s="71"/>
+      <c r="K5" s="19"/>
+    </row>
+    <row r="6" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="72" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="55" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="56"/>
-      <c r="H5" s="50" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51"/>
-      <c r="K5" s="52"/>
-    </row>
-    <row r="6" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="53" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="55" t="s">
+      <c r="C6" s="72"/>
+      <c r="D6" s="72"/>
+      <c r="E6" s="72"/>
+      <c r="F6" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="56"/>
-      <c r="H6" s="50" t="s">
+      <c r="G6" s="75"/>
+      <c r="H6" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="52"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="71"/>
+      <c r="K6" s="19"/>
     </row>
     <row r="7" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="54" t="s">
+      <c r="B7" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="55" t="s">
+      <c r="C7" s="73"/>
+      <c r="D7" s="73"/>
+      <c r="E7" s="73"/>
+      <c r="F7" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="56"/>
-      <c r="H7" s="50" t="s">
+      <c r="G7" s="75"/>
+      <c r="H7" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="I7" s="51"/>
-      <c r="J7" s="51"/>
-      <c r="K7" s="52"/>
+      <c r="I7" s="71"/>
+      <c r="J7" s="71"/>
+      <c r="K7" s="19"/>
     </row>
     <row r="8" spans="1:14" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
@@ -1300,19 +1227,19 @@
       <c r="K8" s="2"/>
     </row>
     <row r="9" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="42" t="s">
+      <c r="A9" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="43"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43"/>
-      <c r="J9" s="43"/>
-      <c r="K9" s="43"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="24"/>
     </row>
     <row r="10" spans="1:14" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
@@ -1328,584 +1255,575 @@
       <c r="K10" s="2"/>
     </row>
     <row r="11" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="73"/>
-      <c r="B11" s="74"/>
-      <c r="C11" s="70" t="s">
+      <c r="A11" s="35"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="72"/>
-      <c r="E11" s="12" t="s">
+      <c r="D11" s="42"/>
+      <c r="E11" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="66" t="s">
+      <c r="F11" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="G11" s="66"/>
-      <c r="H11" s="70" t="s">
+      <c r="G11" s="61"/>
+      <c r="H11" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="I11" s="71"/>
-      <c r="J11" s="71"/>
-      <c r="K11" s="72"/>
+      <c r="I11" s="65"/>
+      <c r="J11" s="65"/>
+      <c r="K11" s="42"/>
     </row>
     <row r="12" spans="1:14" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="75"/>
-      <c r="B12" s="76"/>
-      <c r="C12" s="82"/>
-      <c r="D12" s="82"/>
-      <c r="E12" s="79"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="61"/>
-      <c r="H12" s="60"/>
-      <c r="I12" s="67"/>
-      <c r="J12" s="67"/>
-      <c r="K12" s="61"/>
+      <c r="A12" s="37"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="56"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="62"/>
+      <c r="J12" s="62"/>
+      <c r="K12" s="56"/>
     </row>
     <row r="13" spans="1:14" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="77"/>
-      <c r="B13" s="78"/>
-      <c r="C13" s="82"/>
-      <c r="D13" s="82"/>
-      <c r="E13" s="80"/>
-      <c r="F13" s="62"/>
-      <c r="G13" s="63"/>
-      <c r="H13" s="62"/>
-      <c r="I13" s="68"/>
-      <c r="J13" s="68"/>
-      <c r="K13" s="63"/>
+      <c r="A13" s="39"/>
+      <c r="B13" s="40"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="58"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="63"/>
+      <c r="J13" s="63"/>
+      <c r="K13" s="58"/>
     </row>
     <row r="14" spans="1:14" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="77"/>
-      <c r="B14" s="78"/>
-      <c r="C14" s="82"/>
-      <c r="D14" s="82"/>
-      <c r="E14" s="80"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="63"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="69"/>
-      <c r="J14" s="69"/>
-      <c r="K14" s="65"/>
+      <c r="A14" s="39"/>
+      <c r="B14" s="40"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="58"/>
+      <c r="H14" s="59"/>
+      <c r="I14" s="64"/>
+      <c r="J14" s="64"/>
+      <c r="K14" s="60"/>
     </row>
     <row r="15" spans="1:14" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="77"/>
-      <c r="B15" s="78"/>
-      <c r="C15" s="82"/>
-      <c r="D15" s="82"/>
-      <c r="E15" s="80"/>
-      <c r="F15" s="62"/>
-      <c r="G15" s="63"/>
-      <c r="H15" s="60"/>
-      <c r="I15" s="67"/>
-      <c r="J15" s="67"/>
-      <c r="K15" s="61"/>
+      <c r="A15" s="39"/>
+      <c r="B15" s="40"/>
+      <c r="C15" s="50"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="44"/>
+      <c r="F15" s="57"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="55"/>
+      <c r="I15" s="62"/>
+      <c r="J15" s="62"/>
+      <c r="K15" s="56"/>
     </row>
     <row r="16" spans="1:14" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="77"/>
-      <c r="B16" s="78"/>
-      <c r="C16" s="82"/>
-      <c r="D16" s="82"/>
-      <c r="E16" s="80"/>
-      <c r="F16" s="62"/>
-      <c r="G16" s="63"/>
-      <c r="H16" s="62"/>
-      <c r="I16" s="68"/>
-      <c r="J16" s="68"/>
-      <c r="K16" s="63"/>
+      <c r="A16" s="39"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="57"/>
+      <c r="G16" s="58"/>
+      <c r="H16" s="57"/>
+      <c r="I16" s="63"/>
+      <c r="J16" s="63"/>
+      <c r="K16" s="58"/>
     </row>
     <row r="17" spans="1:11" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="77"/>
-      <c r="B17" s="78"/>
-      <c r="C17" s="82"/>
-      <c r="D17" s="82"/>
-      <c r="E17" s="81"/>
-      <c r="F17" s="64"/>
-      <c r="G17" s="65"/>
-      <c r="H17" s="64"/>
-      <c r="I17" s="69"/>
-      <c r="J17" s="69"/>
-      <c r="K17" s="65"/>
+      <c r="A17" s="39"/>
+      <c r="B17" s="40"/>
+      <c r="C17" s="53"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="59"/>
+      <c r="G17" s="60"/>
+      <c r="H17" s="59"/>
+      <c r="I17" s="64"/>
+      <c r="J17" s="64"/>
+      <c r="K17" s="60"/>
     </row>
     <row r="18" spans="1:11" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="77"/>
-      <c r="B18" s="78"/>
-      <c r="C18" s="82"/>
-      <c r="D18" s="82"/>
-      <c r="E18" s="79"/>
-      <c r="F18" s="60"/>
-      <c r="G18" s="61"/>
-      <c r="H18" s="60"/>
-      <c r="I18" s="67"/>
-      <c r="J18" s="67"/>
-      <c r="K18" s="61"/>
+      <c r="A18" s="39"/>
+      <c r="B18" s="40"/>
+      <c r="C18" s="46"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="55"/>
+      <c r="G18" s="56"/>
+      <c r="H18" s="55"/>
+      <c r="I18" s="62"/>
+      <c r="J18" s="62"/>
+      <c r="K18" s="56"/>
     </row>
     <row r="19" spans="1:11" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="77"/>
-      <c r="B19" s="78"/>
-      <c r="C19" s="82"/>
-      <c r="D19" s="82"/>
-      <c r="E19" s="80"/>
-      <c r="F19" s="62"/>
-      <c r="G19" s="63"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="68"/>
-      <c r="J19" s="68"/>
-      <c r="K19" s="63"/>
+      <c r="A19" s="39"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="63"/>
+      <c r="J19" s="63"/>
+      <c r="K19" s="58"/>
     </row>
     <row r="20" spans="1:11" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="77"/>
-      <c r="B20" s="78"/>
-      <c r="C20" s="82"/>
-      <c r="D20" s="82"/>
-      <c r="E20" s="80"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="63"/>
-      <c r="H20" s="64"/>
-      <c r="I20" s="69"/>
-      <c r="J20" s="69"/>
-      <c r="K20" s="65"/>
+      <c r="A20" s="39"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="48"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="58"/>
+      <c r="H20" s="59"/>
+      <c r="I20" s="64"/>
+      <c r="J20" s="64"/>
+      <c r="K20" s="60"/>
     </row>
     <row r="21" spans="1:11" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="77"/>
-      <c r="B21" s="78"/>
-      <c r="C21" s="82"/>
-      <c r="D21" s="82"/>
-      <c r="E21" s="80"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="63"/>
-      <c r="H21" s="60"/>
-      <c r="I21" s="67"/>
-      <c r="J21" s="67"/>
-      <c r="K21" s="61"/>
+      <c r="A21" s="39"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="50"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="57"/>
+      <c r="G21" s="58"/>
+      <c r="H21" s="55"/>
+      <c r="I21" s="62"/>
+      <c r="J21" s="62"/>
+      <c r="K21" s="56"/>
     </row>
     <row r="22" spans="1:11" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="77"/>
-      <c r="B22" s="78"/>
-      <c r="C22" s="82"/>
-      <c r="D22" s="82"/>
-      <c r="E22" s="80"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="63"/>
-      <c r="H22" s="62"/>
-      <c r="I22" s="68"/>
-      <c r="J22" s="68"/>
-      <c r="K22" s="63"/>
+      <c r="A22" s="39"/>
+      <c r="B22" s="40"/>
+      <c r="C22" s="52"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="57"/>
+      <c r="G22" s="58"/>
+      <c r="H22" s="57"/>
+      <c r="I22" s="63"/>
+      <c r="J22" s="63"/>
+      <c r="K22" s="58"/>
     </row>
     <row r="23" spans="1:11" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="77"/>
-      <c r="B23" s="78"/>
-      <c r="C23" s="82"/>
-      <c r="D23" s="82"/>
-      <c r="E23" s="81"/>
-      <c r="F23" s="64"/>
-      <c r="G23" s="65"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="69"/>
-      <c r="J23" s="69"/>
-      <c r="K23" s="65"/>
+      <c r="A23" s="39"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="53"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="59"/>
+      <c r="G23" s="60"/>
+      <c r="H23" s="59"/>
+      <c r="I23" s="64"/>
+      <c r="J23" s="64"/>
+      <c r="K23" s="60"/>
     </row>
     <row r="24" spans="1:11" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="77"/>
-      <c r="B24" s="78"/>
-      <c r="C24" s="82"/>
-      <c r="D24" s="82"/>
-      <c r="E24" s="79"/>
-      <c r="F24" s="60"/>
-      <c r="G24" s="61"/>
-      <c r="H24" s="60"/>
-      <c r="I24" s="67"/>
-      <c r="J24" s="67"/>
-      <c r="K24" s="61"/>
+      <c r="A24" s="39"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="55"/>
+      <c r="G24" s="56"/>
+      <c r="H24" s="55"/>
+      <c r="I24" s="62"/>
+      <c r="J24" s="62"/>
+      <c r="K24" s="56"/>
     </row>
     <row r="25" spans="1:11" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="77"/>
-      <c r="B25" s="78"/>
-      <c r="C25" s="82"/>
-      <c r="D25" s="82"/>
-      <c r="E25" s="80"/>
-      <c r="F25" s="62"/>
-      <c r="G25" s="63"/>
-      <c r="H25" s="62"/>
-      <c r="I25" s="68"/>
-      <c r="J25" s="68"/>
-      <c r="K25" s="63"/>
+      <c r="A25" s="39"/>
+      <c r="B25" s="40"/>
+      <c r="C25" s="48"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="58"/>
+      <c r="H25" s="57"/>
+      <c r="I25" s="63"/>
+      <c r="J25" s="63"/>
+      <c r="K25" s="58"/>
     </row>
     <row r="26" spans="1:11" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="77"/>
-      <c r="B26" s="78"/>
-      <c r="C26" s="82"/>
-      <c r="D26" s="82"/>
-      <c r="E26" s="80"/>
-      <c r="F26" s="62"/>
-      <c r="G26" s="63"/>
-      <c r="H26" s="64"/>
-      <c r="I26" s="69"/>
-      <c r="J26" s="69"/>
-      <c r="K26" s="65"/>
+      <c r="A26" s="39"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="58"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="64"/>
+      <c r="J26" s="64"/>
+      <c r="K26" s="60"/>
     </row>
     <row r="27" spans="1:11" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="77"/>
-      <c r="B27" s="78"/>
-      <c r="C27" s="82"/>
-      <c r="D27" s="82"/>
-      <c r="E27" s="80"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="63"/>
-      <c r="H27" s="60"/>
-      <c r="I27" s="67"/>
-      <c r="J27" s="67"/>
-      <c r="K27" s="61"/>
+      <c r="A27" s="39"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="50"/>
+      <c r="D27" s="51"/>
+      <c r="E27" s="44"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="58"/>
+      <c r="H27" s="55"/>
+      <c r="I27" s="62"/>
+      <c r="J27" s="62"/>
+      <c r="K27" s="56"/>
     </row>
     <row r="28" spans="1:11" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="77"/>
-      <c r="B28" s="78"/>
-      <c r="C28" s="82"/>
-      <c r="D28" s="82"/>
-      <c r="E28" s="80"/>
-      <c r="F28" s="62"/>
-      <c r="G28" s="63"/>
-      <c r="H28" s="62"/>
-      <c r="I28" s="68"/>
-      <c r="J28" s="68"/>
-      <c r="K28" s="63"/>
+      <c r="A28" s="39"/>
+      <c r="B28" s="40"/>
+      <c r="C28" s="52"/>
+      <c r="D28" s="51"/>
+      <c r="E28" s="44"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="58"/>
+      <c r="H28" s="57"/>
+      <c r="I28" s="63"/>
+      <c r="J28" s="63"/>
+      <c r="K28" s="58"/>
     </row>
     <row r="29" spans="1:11" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="77"/>
-      <c r="B29" s="78"/>
-      <c r="C29" s="83"/>
-      <c r="D29" s="83"/>
-      <c r="E29" s="80"/>
-      <c r="F29" s="62"/>
-      <c r="G29" s="63"/>
-      <c r="H29" s="62"/>
-      <c r="I29" s="68"/>
-      <c r="J29" s="68"/>
-      <c r="K29" s="63"/>
+      <c r="A29" s="39"/>
+      <c r="B29" s="40"/>
+      <c r="C29" s="53"/>
+      <c r="D29" s="54"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="59"/>
+      <c r="G29" s="60"/>
+      <c r="H29" s="59"/>
+      <c r="I29" s="64"/>
+      <c r="J29" s="64"/>
+      <c r="K29" s="60"/>
     </row>
     <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="B30" s="20"/>
-      <c r="C30" s="21" t="s">
+      <c r="B30" s="83"/>
+      <c r="C30" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="21"/>
-      <c r="I30" s="21"/>
-      <c r="J30" s="21"/>
-      <c r="K30" s="21"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="22"/>
+      <c r="K30" s="22"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A31" s="20"/>
-      <c r="B31" s="20"/>
-      <c r="C31" s="21"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="21"/>
-      <c r="G31" s="21"/>
-      <c r="H31" s="21"/>
-      <c r="I31" s="21"/>
-      <c r="J31" s="21"/>
-      <c r="K31" s="21"/>
+      <c r="A31" s="83"/>
+      <c r="B31" s="83"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="22"/>
+      <c r="K31" s="22"/>
     </row>
     <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="33" t="s">
+      <c r="A32" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="B32" s="34"/>
-      <c r="C32" s="39"/>
-      <c r="D32" s="39"/>
-      <c r="E32" s="96" t="s">
+      <c r="B32" s="85"/>
+      <c r="C32" s="83"/>
+      <c r="D32" s="83"/>
+      <c r="E32" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F32" s="97" t="s">
+      <c r="F32" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="G32" s="24"/>
+      <c r="H32" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="I32" s="21"/>
+      <c r="J32" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="K32" s="24"/>
+    </row>
+    <row r="33" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="86"/>
+      <c r="B33" s="87"/>
+      <c r="C33" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" s="91"/>
+      <c r="E33" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G32" s="97"/>
-      <c r="H32" s="97" t="s">
-        <v>46</v>
-      </c>
-      <c r="I32" s="97"/>
-      <c r="J32" s="97" t="s">
+      <c r="F33" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="G33" s="20"/>
+      <c r="H33" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I33" s="20"/>
+      <c r="J33" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="K33" s="22"/>
+    </row>
+    <row r="34" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="88"/>
+      <c r="B34" s="89"/>
+      <c r="C34" s="90" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="91"/>
+      <c r="E34" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F34" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G34" s="20"/>
+      <c r="H34" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="I34" s="20"/>
+      <c r="J34" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="K34" s="22"/>
+    </row>
+    <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B35" s="83"/>
+      <c r="C35" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="D35" s="24"/>
+      <c r="E35" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="F35" s="25"/>
+      <c r="G35" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="H35" s="24"/>
+      <c r="I35" s="24"/>
+      <c r="J35" s="24"/>
+      <c r="K35" s="24"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A36" s="83"/>
+      <c r="B36" s="83"/>
+      <c r="C36" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="K32" s="97"/>
-    </row>
-    <row r="33" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="35"/>
-      <c r="B33" s="36"/>
-      <c r="C33" s="99" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" s="100"/>
-      <c r="E33" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="F33" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="G33" s="41"/>
-      <c r="H33" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="I33" s="41"/>
-      <c r="J33" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="K33" s="95"/>
-    </row>
-    <row r="34" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="37"/>
-      <c r="B34" s="38"/>
-      <c r="C34" s="99" t="s">
-        <v>21</v>
-      </c>
-      <c r="D34" s="100"/>
-      <c r="E34" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="F34" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="G34" s="41"/>
-      <c r="H34" s="40" t="s">
-        <v>48</v>
-      </c>
-      <c r="I34" s="41"/>
-      <c r="J34" s="40" t="s">
-        <v>45</v>
-      </c>
-      <c r="K34" s="95"/>
-    </row>
-    <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B35" s="32"/>
-      <c r="C35" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D35" s="31"/>
-      <c r="E35" s="98" t="s">
+      <c r="D36" s="22"/>
+      <c r="E36" s="23">
+        <v>0.99652777777777779</v>
+      </c>
+      <c r="F36" s="23"/>
+      <c r="G36" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="H36" s="22"/>
+      <c r="I36" s="22"/>
+      <c r="J36" s="22"/>
+      <c r="K36" s="22"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A37" s="83"/>
+      <c r="B37" s="83"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="22"/>
+      <c r="K37" s="22"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A38" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B38" s="24"/>
+      <c r="C38" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="F35" s="98"/>
-      <c r="G35" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="H35" s="31"/>
-      <c r="I35" s="31"/>
-      <c r="J35" s="31"/>
-      <c r="K35" s="31"/>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A36" s="32"/>
-      <c r="B36" s="32"/>
-      <c r="C36" s="93" t="s">
-        <v>38</v>
-      </c>
-      <c r="D36" s="93"/>
-      <c r="E36" s="94">
-        <v>0.99652777777777779</v>
-      </c>
-      <c r="F36" s="94"/>
-      <c r="G36" s="93" t="s">
-        <v>39</v>
-      </c>
-      <c r="H36" s="93"/>
-      <c r="I36" s="93"/>
-      <c r="J36" s="93"/>
-      <c r="K36" s="93"/>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A37" s="32"/>
-      <c r="B37" s="32"/>
-      <c r="C37" s="93"/>
-      <c r="D37" s="93"/>
-      <c r="E37" s="94"/>
-      <c r="F37" s="94"/>
-      <c r="G37" s="93"/>
-      <c r="H37" s="93"/>
-      <c r="I37" s="93"/>
-      <c r="J37" s="93"/>
-      <c r="K37" s="93"/>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A38" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="B38" s="17"/>
-      <c r="C38" s="84" t="s">
-        <v>43</v>
-      </c>
-      <c r="D38" s="85"/>
-      <c r="E38" s="85"/>
-      <c r="F38" s="85"/>
-      <c r="G38" s="85"/>
-      <c r="H38" s="85"/>
-      <c r="I38" s="85"/>
-      <c r="J38" s="85"/>
-      <c r="K38" s="86"/>
+      <c r="D38" s="27"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="27"/>
+      <c r="G38" s="27"/>
+      <c r="H38" s="27"/>
+      <c r="I38" s="27"/>
+      <c r="J38" s="27"/>
+      <c r="K38" s="28"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A39" s="17"/>
-      <c r="B39" s="17"/>
-      <c r="C39" s="87" t="s">
+      <c r="A39" s="24"/>
+      <c r="B39" s="24"/>
+      <c r="C39" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="D39" s="88"/>
-      <c r="E39" s="88"/>
-      <c r="F39" s="88"/>
-      <c r="G39" s="88"/>
-      <c r="H39" s="88"/>
-      <c r="I39" s="88"/>
-      <c r="J39" s="88"/>
-      <c r="K39" s="89"/>
+      <c r="D39" s="30"/>
+      <c r="E39" s="30"/>
+      <c r="F39" s="30"/>
+      <c r="G39" s="30"/>
+      <c r="H39" s="30"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="30"/>
+      <c r="K39" s="31"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A40" s="17"/>
-      <c r="B40" s="17"/>
-      <c r="C40" s="87" t="s">
+      <c r="A40" s="24"/>
+      <c r="B40" s="24"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="30"/>
+      <c r="K40" s="31"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A41" s="24"/>
+      <c r="B41" s="24"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="33"/>
+      <c r="E41" s="33"/>
+      <c r="F41" s="33"/>
+      <c r="G41" s="33"/>
+      <c r="H41" s="33"/>
+      <c r="I41" s="33"/>
+      <c r="J41" s="33"/>
+      <c r="K41" s="34"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A42" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B42" s="24"/>
+      <c r="C42" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="D42" s="62"/>
+      <c r="E42" s="62"/>
+      <c r="F42" s="62"/>
+      <c r="G42" s="62"/>
+      <c r="H42" s="62"/>
+      <c r="I42" s="62"/>
+      <c r="J42" s="62"/>
+      <c r="K42" s="56"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A43" s="24"/>
+      <c r="B43" s="24"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="31"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A44" s="24"/>
+      <c r="B44" s="24"/>
+      <c r="C44" s="29"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="30"/>
+      <c r="G44" s="30"/>
+      <c r="H44" s="30"/>
+      <c r="I44" s="30"/>
+      <c r="J44" s="30"/>
+      <c r="K44" s="31"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A45" s="24"/>
+      <c r="B45" s="24"/>
+      <c r="C45" s="32"/>
+      <c r="D45" s="33"/>
+      <c r="E45" s="33"/>
+      <c r="F45" s="33"/>
+      <c r="G45" s="33"/>
+      <c r="H45" s="33"/>
+      <c r="I45" s="33"/>
+      <c r="J45" s="33"/>
+      <c r="K45" s="34"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A46" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B46" s="24"/>
+      <c r="C46" s="81" t="s">
         <v>29</v>
       </c>
-      <c r="D40" s="88"/>
-      <c r="E40" s="88"/>
-      <c r="F40" s="88"/>
-      <c r="G40" s="88"/>
-      <c r="H40" s="88"/>
-      <c r="I40" s="88"/>
-      <c r="J40" s="88"/>
-      <c r="K40" s="89"/>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A41" s="17"/>
-      <c r="B41" s="17"/>
-      <c r="C41" s="90"/>
-      <c r="D41" s="91"/>
-      <c r="E41" s="91"/>
-      <c r="F41" s="91"/>
-      <c r="G41" s="91"/>
-      <c r="H41" s="91"/>
-      <c r="I41" s="91"/>
-      <c r="J41" s="91"/>
-      <c r="K41" s="92"/>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A42" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="B42" s="17"/>
-      <c r="C42" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="D42" s="23"/>
-      <c r="E42" s="23"/>
-      <c r="F42" s="23"/>
-      <c r="G42" s="23"/>
-      <c r="H42" s="23"/>
-      <c r="I42" s="23"/>
-      <c r="J42" s="23"/>
-      <c r="K42" s="24"/>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A43" s="17"/>
-      <c r="B43" s="17"/>
-      <c r="C43" s="25"/>
-      <c r="D43" s="26"/>
-      <c r="E43" s="26"/>
-      <c r="F43" s="26"/>
-      <c r="G43" s="26"/>
-      <c r="H43" s="26"/>
-      <c r="I43" s="26"/>
-      <c r="J43" s="26"/>
-      <c r="K43" s="27"/>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A44" s="17"/>
-      <c r="B44" s="17"/>
-      <c r="C44" s="28"/>
-      <c r="D44" s="29"/>
-      <c r="E44" s="29"/>
-      <c r="F44" s="29"/>
-      <c r="G44" s="29"/>
-      <c r="H44" s="29"/>
-      <c r="I44" s="29"/>
-      <c r="J44" s="29"/>
-      <c r="K44" s="30"/>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A45" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="B45" s="17"/>
-      <c r="C45" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="D45" s="19"/>
-      <c r="E45" s="19"/>
-      <c r="F45" s="19"/>
-      <c r="G45" s="19"/>
-      <c r="H45" s="19"/>
-      <c r="I45" s="19"/>
-      <c r="J45" s="19"/>
-      <c r="K45" s="19"/>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A46" s="17"/>
-      <c r="B46" s="17"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
-      <c r="H46" s="19"/>
-      <c r="I46" s="19"/>
-      <c r="J46" s="19"/>
-      <c r="K46" s="19"/>
+      <c r="D46" s="82"/>
+      <c r="E46" s="82"/>
+      <c r="F46" s="82"/>
+      <c r="G46" s="82"/>
+      <c r="H46" s="82"/>
+      <c r="I46" s="82"/>
+      <c r="J46" s="82"/>
+      <c r="K46" s="82"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A47" s="24"/>
+      <c r="B47" s="24"/>
+      <c r="C47" s="82"/>
+      <c r="D47" s="82"/>
+      <c r="E47" s="82"/>
+      <c r="F47" s="82"/>
+      <c r="G47" s="82"/>
+      <c r="H47" s="82"/>
+      <c r="I47" s="82"/>
+      <c r="J47" s="82"/>
+      <c r="K47" s="82"/>
     </row>
   </sheetData>
-  <mergeCells count="67">
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="C36:D37"/>
-    <mergeCell ref="E36:F37"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="G35:K35"/>
-    <mergeCell ref="G36:K37"/>
-    <mergeCell ref="A38:B41"/>
-    <mergeCell ref="C38:K38"/>
-    <mergeCell ref="C39:K39"/>
-    <mergeCell ref="C40:K40"/>
-    <mergeCell ref="C41:K41"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B29"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E12:E17"/>
-    <mergeCell ref="E18:E23"/>
-    <mergeCell ref="E24:E29"/>
-    <mergeCell ref="C12:D17"/>
-    <mergeCell ref="C18:D23"/>
-    <mergeCell ref="C24:D29"/>
-    <mergeCell ref="F12:G17"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F18:G23"/>
-    <mergeCell ref="F24:G29"/>
-    <mergeCell ref="H12:K14"/>
-    <mergeCell ref="H15:K17"/>
-    <mergeCell ref="H18:K20"/>
-    <mergeCell ref="H21:K23"/>
-    <mergeCell ref="H24:K26"/>
-    <mergeCell ref="H27:K29"/>
-    <mergeCell ref="H11:K11"/>
+  <mergeCells count="71">
+    <mergeCell ref="C44:K44"/>
+    <mergeCell ref="A46:B47"/>
+    <mergeCell ref="C46:K47"/>
+    <mergeCell ref="A30:B31"/>
+    <mergeCell ref="C30:K31"/>
+    <mergeCell ref="A42:B45"/>
+    <mergeCell ref="C42:K42"/>
+    <mergeCell ref="C43:K43"/>
+    <mergeCell ref="C45:K45"/>
+    <mergeCell ref="A35:B37"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="A32:B34"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="F33:G33"/>
     <mergeCell ref="A9:K9"/>
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="A3:K3"/>
@@ -1920,22 +1838,46 @@
     <mergeCell ref="H7:K7"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:E2"/>
-    <mergeCell ref="A45:B46"/>
-    <mergeCell ref="C45:K46"/>
-    <mergeCell ref="A30:B31"/>
-    <mergeCell ref="C30:K31"/>
-    <mergeCell ref="A42:B44"/>
-    <mergeCell ref="C42:K42"/>
-    <mergeCell ref="C43:K43"/>
-    <mergeCell ref="C44:K44"/>
-    <mergeCell ref="A35:B37"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="A32:B34"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F12:G17"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F18:G23"/>
+    <mergeCell ref="F24:G29"/>
+    <mergeCell ref="H12:K14"/>
+    <mergeCell ref="H15:K17"/>
+    <mergeCell ref="H18:K20"/>
+    <mergeCell ref="H21:K23"/>
+    <mergeCell ref="H24:K26"/>
+    <mergeCell ref="H27:K29"/>
+    <mergeCell ref="H11:K11"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B29"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E12:E17"/>
+    <mergeCell ref="E18:E23"/>
+    <mergeCell ref="E24:E29"/>
+    <mergeCell ref="C12:D14"/>
+    <mergeCell ref="C15:D17"/>
+    <mergeCell ref="C18:D20"/>
+    <mergeCell ref="C21:D23"/>
+    <mergeCell ref="C24:D26"/>
+    <mergeCell ref="C27:D29"/>
+    <mergeCell ref="A38:B41"/>
+    <mergeCell ref="C38:K38"/>
+    <mergeCell ref="C39:K39"/>
+    <mergeCell ref="C40:K40"/>
+    <mergeCell ref="C41:K41"/>
+    <mergeCell ref="C36:D37"/>
+    <mergeCell ref="E36:F37"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="G35:K35"/>
+    <mergeCell ref="G36:K37"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" orientation="portrait" r:id="rId1"/>

--- a/Template/Voucher Template.xlsx
+++ b/Template/Voucher Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Smart Travel PC\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Smart Travel PC\Desktop\Vouchers Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71E23664-119A-47C9-88C0-F339A9350669}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC047EC8-AB16-4218-A569-6B5882E2D2B6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="45" windowWidth="10860" windowHeight="15705" xr2:uid="{46FCF62E-0F38-40EF-B40B-6239A54C7BFA}"/>
+    <workbookView xWindow="1950" yWindow="675" windowWidth="19935" windowHeight="15525" xr2:uid="{46FCF62E-0F38-40EF-B40B-6239A54C7BFA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -114,9 +114,6 @@
     <t>Meals (4 times Lunch, 4 times Dinner)</t>
   </si>
   <si>
-    <t>*** It will be subject to change as the local situation ***</t>
-  </si>
-  <si>
     <t>FLIGHT:</t>
   </si>
   <si>
@@ -169,6 +166,9 @@
   </si>
   <si>
     <t>ICN - MNL</t>
+  </si>
+  <si>
+    <t>*** It will be subject to change based on the local situation ***</t>
   </si>
 </sst>
 </file>
@@ -488,36 +488,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -527,6 +497,30 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -536,9 +530,114 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -554,10 +653,10 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -596,116 +695,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -728,23 +728,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>85724</xdr:rowOff>
+      <xdr:rowOff>19049</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>742949</xdr:rowOff>
+      <xdr:rowOff>723900</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4082659-BA31-48F8-A3BA-47100248BF8C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0BDFC6A-3B55-4B5E-ABF3-1BFC47E49B9C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -753,20 +753,20 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:srcRect t="8140" r="1240" b="3488"/>
+        <a:srcRect l="14562" t="38950" r="24164" b="43105"/>
         <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="38100" y="85724"/>
-          <a:ext cx="6257925" cy="657225"/>
+          <a:off x="1752600" y="19049"/>
+          <a:ext cx="2924175" cy="704851"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1075,21 +1075,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E608D469-AF7C-422E-92CF-2B4802A6A2AF}">
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="8" style="3" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" style="3" customWidth="1"/>
     <col min="3" max="3" width="7.28515625" style="3" customWidth="1"/>
     <col min="4" max="4" width="8.42578125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="11.140625" style="3" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="3"/>
-    <col min="7" max="7" width="8.28515625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="7.85546875" style="3" customWidth="1"/>
     <col min="8" max="10" width="9.140625" style="3"/>
-    <col min="11" max="11" width="9.140625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="3" customWidth="1"/>
     <col min="12" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="81" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="68.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1103,37 +1104,37 @@
       <c r="K1" s="2"/>
     </row>
     <row r="2" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="76" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="77"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="80"/>
+      <c r="A2" s="54" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="55"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="58"/>
       <c r="F2" s="13"/>
       <c r="G2" s="14"/>
       <c r="H2" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="66"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="68"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="43"/>
       <c r="N2" s="2"/>
     </row>
     <row r="3" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="69"/>
-      <c r="K3" s="70"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="46"/>
       <c r="N3" s="2"/>
     </row>
     <row r="4" spans="1:14" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1150,68 +1151,68 @@
       <c r="K4" s="9"/>
       <c r="N4" s="2"/>
     </row>
-    <row r="5" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="72" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="72"/>
-      <c r="D5" s="72"/>
-      <c r="E5" s="72"/>
-      <c r="F5" s="74" t="s">
+      <c r="B5" s="50" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="50"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="75"/>
-      <c r="H5" s="20" t="s">
+      <c r="G5" s="53"/>
+      <c r="H5" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="71"/>
-      <c r="J5" s="71"/>
-      <c r="K5" s="19"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="49"/>
     </row>
     <row r="6" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="72" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="72"/>
-      <c r="D6" s="72"/>
-      <c r="E6" s="72"/>
-      <c r="F6" s="74" t="s">
+      <c r="B6" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="50"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="75"/>
-      <c r="H6" s="20" t="s">
+      <c r="G6" s="53"/>
+      <c r="H6" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="71"/>
-      <c r="J6" s="71"/>
-      <c r="K6" s="19"/>
-    </row>
-    <row r="7" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="49"/>
+    </row>
+    <row r="7" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="73" t="s">
+      <c r="B7" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="73"/>
-      <c r="D7" s="73"/>
-      <c r="E7" s="73"/>
-      <c r="F7" s="74" t="s">
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="75"/>
-      <c r="H7" s="20" t="s">
+      <c r="G7" s="53"/>
+      <c r="H7" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="I7" s="71"/>
-      <c r="J7" s="71"/>
-      <c r="K7" s="19"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="48"/>
+      <c r="K7" s="49"/>
     </row>
     <row r="8" spans="1:14" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
@@ -1227,19 +1228,19 @@
       <c r="K8" s="2"/>
     </row>
     <row r="9" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="24"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="24"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="24"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="22"/>
     </row>
     <row r="10" spans="1:14" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
@@ -1255,575 +1256,600 @@
       <c r="K10" s="2"/>
     </row>
     <row r="11" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="35"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="41" t="s">
+      <c r="A11" s="44"/>
+      <c r="B11" s="69"/>
+      <c r="C11" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="42"/>
+      <c r="D11" s="68"/>
       <c r="E11" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="61" t="s">
+      <c r="F11" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="G11" s="61"/>
-      <c r="H11" s="41" t="s">
+      <c r="G11" s="59"/>
+      <c r="H11" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="I11" s="65"/>
-      <c r="J11" s="65"/>
-      <c r="K11" s="42"/>
-    </row>
-    <row r="12" spans="1:14" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="37"/>
-      <c r="B12" s="38"/>
-      <c r="C12" s="46"/>
-      <c r="D12" s="47"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="56"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="62"/>
-      <c r="J12" s="62"/>
-      <c r="K12" s="56"/>
-    </row>
-    <row r="13" spans="1:14" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="39"/>
-      <c r="B13" s="40"/>
-      <c r="C13" s="48"/>
-      <c r="D13" s="49"/>
-      <c r="E13" s="44"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="58"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="63"/>
-      <c r="J13" s="63"/>
-      <c r="K13" s="58"/>
-    </row>
-    <row r="14" spans="1:14" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="39"/>
-      <c r="B14" s="40"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="58"/>
-      <c r="H14" s="59"/>
-      <c r="I14" s="64"/>
-      <c r="J14" s="64"/>
-      <c r="K14" s="60"/>
-    </row>
-    <row r="15" spans="1:14" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="39"/>
-      <c r="B15" s="40"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="51"/>
-      <c r="E15" s="44"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="58"/>
-      <c r="H15" s="55"/>
-      <c r="I15" s="62"/>
-      <c r="J15" s="62"/>
-      <c r="K15" s="56"/>
-    </row>
-    <row r="16" spans="1:14" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="39"/>
-      <c r="B16" s="40"/>
-      <c r="C16" s="52"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="57"/>
-      <c r="G16" s="58"/>
-      <c r="H16" s="57"/>
-      <c r="I16" s="63"/>
-      <c r="J16" s="63"/>
-      <c r="K16" s="58"/>
-    </row>
-    <row r="17" spans="1:11" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="39"/>
-      <c r="B17" s="40"/>
-      <c r="C17" s="53"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="45"/>
-      <c r="F17" s="59"/>
-      <c r="G17" s="60"/>
-      <c r="H17" s="59"/>
-      <c r="I17" s="64"/>
-      <c r="J17" s="64"/>
-      <c r="K17" s="60"/>
-    </row>
-    <row r="18" spans="1:11" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="39"/>
-      <c r="B18" s="40"/>
-      <c r="C18" s="46"/>
-      <c r="D18" s="47"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="55"/>
-      <c r="G18" s="56"/>
-      <c r="H18" s="55"/>
-      <c r="I18" s="62"/>
-      <c r="J18" s="62"/>
-      <c r="K18" s="56"/>
-    </row>
-    <row r="19" spans="1:11" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="39"/>
-      <c r="B19" s="40"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="49"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="58"/>
-      <c r="H19" s="57"/>
-      <c r="I19" s="63"/>
-      <c r="J19" s="63"/>
-      <c r="K19" s="58"/>
-    </row>
-    <row r="20" spans="1:11" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="39"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="48"/>
-      <c r="D20" s="49"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="57"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="59"/>
-      <c r="I20" s="64"/>
-      <c r="J20" s="64"/>
-      <c r="K20" s="60"/>
-    </row>
-    <row r="21" spans="1:11" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="39"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="50"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="57"/>
-      <c r="G21" s="58"/>
-      <c r="H21" s="55"/>
-      <c r="I21" s="62"/>
-      <c r="J21" s="62"/>
-      <c r="K21" s="56"/>
-    </row>
-    <row r="22" spans="1:11" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="39"/>
-      <c r="B22" s="40"/>
-      <c r="C22" s="52"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="44"/>
-      <c r="F22" s="57"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="57"/>
-      <c r="I22" s="63"/>
-      <c r="J22" s="63"/>
-      <c r="K22" s="58"/>
-    </row>
-    <row r="23" spans="1:11" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="39"/>
-      <c r="B23" s="40"/>
-      <c r="C23" s="53"/>
-      <c r="D23" s="54"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="59"/>
-      <c r="G23" s="60"/>
-      <c r="H23" s="59"/>
-      <c r="I23" s="64"/>
-      <c r="J23" s="64"/>
-      <c r="K23" s="60"/>
-    </row>
-    <row r="24" spans="1:11" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="39"/>
-      <c r="B24" s="40"/>
-      <c r="C24" s="46"/>
-      <c r="D24" s="47"/>
-      <c r="E24" s="43"/>
-      <c r="F24" s="55"/>
-      <c r="G24" s="56"/>
-      <c r="H24" s="55"/>
-      <c r="I24" s="62"/>
-      <c r="J24" s="62"/>
-      <c r="K24" s="56"/>
-    </row>
-    <row r="25" spans="1:11" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="39"/>
-      <c r="B25" s="40"/>
-      <c r="C25" s="48"/>
-      <c r="D25" s="49"/>
-      <c r="E25" s="44"/>
-      <c r="F25" s="57"/>
-      <c r="G25" s="58"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="63"/>
-      <c r="J25" s="63"/>
-      <c r="K25" s="58"/>
-    </row>
-    <row r="26" spans="1:11" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="39"/>
-      <c r="B26" s="40"/>
-      <c r="C26" s="48"/>
-      <c r="D26" s="49"/>
-      <c r="E26" s="44"/>
-      <c r="F26" s="57"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="59"/>
-      <c r="I26" s="64"/>
-      <c r="J26" s="64"/>
-      <c r="K26" s="60"/>
-    </row>
-    <row r="27" spans="1:11" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="39"/>
-      <c r="B27" s="40"/>
-      <c r="C27" s="50"/>
-      <c r="D27" s="51"/>
-      <c r="E27" s="44"/>
-      <c r="F27" s="57"/>
-      <c r="G27" s="58"/>
-      <c r="H27" s="55"/>
-      <c r="I27" s="62"/>
-      <c r="J27" s="62"/>
-      <c r="K27" s="56"/>
-    </row>
-    <row r="28" spans="1:11" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="39"/>
-      <c r="B28" s="40"/>
-      <c r="C28" s="52"/>
-      <c r="D28" s="51"/>
-      <c r="E28" s="44"/>
-      <c r="F28" s="57"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="57"/>
-      <c r="I28" s="63"/>
-      <c r="J28" s="63"/>
-      <c r="K28" s="58"/>
-    </row>
-    <row r="29" spans="1:11" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="39"/>
-      <c r="B29" s="40"/>
-      <c r="C29" s="53"/>
-      <c r="D29" s="54"/>
-      <c r="E29" s="45"/>
-      <c r="F29" s="59"/>
-      <c r="G29" s="60"/>
-      <c r="H29" s="59"/>
-      <c r="I29" s="64"/>
-      <c r="J29" s="64"/>
-      <c r="K29" s="60"/>
-    </row>
-    <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="24" t="s">
+      <c r="I11" s="67"/>
+      <c r="J11" s="67"/>
+      <c r="K11" s="68"/>
+    </row>
+    <row r="12" spans="1:14" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="70"/>
+      <c r="B12" s="71"/>
+      <c r="C12" s="79"/>
+      <c r="D12" s="80"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="28"/>
+      <c r="K12" s="29"/>
+    </row>
+    <row r="13" spans="1:14" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="72"/>
+      <c r="B13" s="73"/>
+      <c r="C13" s="81"/>
+      <c r="D13" s="82"/>
+      <c r="E13" s="77"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="64"/>
+      <c r="J13" s="64"/>
+      <c r="K13" s="61"/>
+    </row>
+    <row r="14" spans="1:14" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="72"/>
+      <c r="B14" s="73"/>
+      <c r="C14" s="81"/>
+      <c r="D14" s="82"/>
+      <c r="E14" s="77"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="65"/>
+      <c r="J14" s="65"/>
+      <c r="K14" s="63"/>
+    </row>
+    <row r="15" spans="1:14" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="72"/>
+      <c r="B15" s="73"/>
+      <c r="C15" s="83"/>
+      <c r="D15" s="84"/>
+      <c r="E15" s="77"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="29"/>
+    </row>
+    <row r="16" spans="1:14" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="72"/>
+      <c r="B16" s="73"/>
+      <c r="C16" s="85"/>
+      <c r="D16" s="84"/>
+      <c r="E16" s="77"/>
+      <c r="F16" s="60"/>
+      <c r="G16" s="61"/>
+      <c r="H16" s="60"/>
+      <c r="I16" s="64"/>
+      <c r="J16" s="64"/>
+      <c r="K16" s="61"/>
+    </row>
+    <row r="17" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="72"/>
+      <c r="B17" s="73"/>
+      <c r="C17" s="86"/>
+      <c r="D17" s="87"/>
+      <c r="E17" s="78"/>
+      <c r="F17" s="62"/>
+      <c r="G17" s="63"/>
+      <c r="H17" s="62"/>
+      <c r="I17" s="65"/>
+      <c r="J17" s="65"/>
+      <c r="K17" s="63"/>
+    </row>
+    <row r="18" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="72"/>
+      <c r="B18" s="73"/>
+      <c r="C18" s="79"/>
+      <c r="D18" s="80"/>
+      <c r="E18" s="76"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="28"/>
+      <c r="K18" s="29"/>
+    </row>
+    <row r="19" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="72"/>
+      <c r="B19" s="73"/>
+      <c r="C19" s="81"/>
+      <c r="D19" s="82"/>
+      <c r="E19" s="77"/>
+      <c r="F19" s="60"/>
+      <c r="G19" s="61"/>
+      <c r="H19" s="60"/>
+      <c r="I19" s="64"/>
+      <c r="J19" s="64"/>
+      <c r="K19" s="61"/>
+    </row>
+    <row r="20" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="72"/>
+      <c r="B20" s="73"/>
+      <c r="C20" s="81"/>
+      <c r="D20" s="82"/>
+      <c r="E20" s="77"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="61"/>
+      <c r="H20" s="62"/>
+      <c r="I20" s="65"/>
+      <c r="J20" s="65"/>
+      <c r="K20" s="63"/>
+    </row>
+    <row r="21" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="72"/>
+      <c r="B21" s="73"/>
+      <c r="C21" s="83"/>
+      <c r="D21" s="84"/>
+      <c r="E21" s="77"/>
+      <c r="F21" s="60"/>
+      <c r="G21" s="61"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="28"/>
+      <c r="J21" s="28"/>
+      <c r="K21" s="29"/>
+    </row>
+    <row r="22" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="72"/>
+      <c r="B22" s="73"/>
+      <c r="C22" s="85"/>
+      <c r="D22" s="84"/>
+      <c r="E22" s="77"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="61"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="64"/>
+      <c r="J22" s="64"/>
+      <c r="K22" s="61"/>
+    </row>
+    <row r="23" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="72"/>
+      <c r="B23" s="73"/>
+      <c r="C23" s="86"/>
+      <c r="D23" s="87"/>
+      <c r="E23" s="78"/>
+      <c r="F23" s="62"/>
+      <c r="G23" s="63"/>
+      <c r="H23" s="62"/>
+      <c r="I23" s="65"/>
+      <c r="J23" s="65"/>
+      <c r="K23" s="63"/>
+    </row>
+    <row r="24" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="72"/>
+      <c r="B24" s="73"/>
+      <c r="C24" s="79"/>
+      <c r="D24" s="80"/>
+      <c r="E24" s="76"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="28"/>
+      <c r="J24" s="28"/>
+      <c r="K24" s="29"/>
+    </row>
+    <row r="25" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="72"/>
+      <c r="B25" s="73"/>
+      <c r="C25" s="81"/>
+      <c r="D25" s="82"/>
+      <c r="E25" s="77"/>
+      <c r="F25" s="60"/>
+      <c r="G25" s="61"/>
+      <c r="H25" s="60"/>
+      <c r="I25" s="64"/>
+      <c r="J25" s="64"/>
+      <c r="K25" s="61"/>
+    </row>
+    <row r="26" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="72"/>
+      <c r="B26" s="73"/>
+      <c r="C26" s="81"/>
+      <c r="D26" s="82"/>
+      <c r="E26" s="77"/>
+      <c r="F26" s="60"/>
+      <c r="G26" s="61"/>
+      <c r="H26" s="62"/>
+      <c r="I26" s="65"/>
+      <c r="J26" s="65"/>
+      <c r="K26" s="63"/>
+    </row>
+    <row r="27" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="72"/>
+      <c r="B27" s="73"/>
+      <c r="C27" s="83"/>
+      <c r="D27" s="84"/>
+      <c r="E27" s="77"/>
+      <c r="F27" s="60"/>
+      <c r="G27" s="61"/>
+      <c r="H27" s="27"/>
+      <c r="I27" s="28"/>
+      <c r="J27" s="28"/>
+      <c r="K27" s="29"/>
+    </row>
+    <row r="28" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="72"/>
+      <c r="B28" s="73"/>
+      <c r="C28" s="85"/>
+      <c r="D28" s="84"/>
+      <c r="E28" s="77"/>
+      <c r="F28" s="60"/>
+      <c r="G28" s="61"/>
+      <c r="H28" s="60"/>
+      <c r="I28" s="64"/>
+      <c r="J28" s="64"/>
+      <c r="K28" s="61"/>
+    </row>
+    <row r="29" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="74"/>
+      <c r="B29" s="75"/>
+      <c r="C29" s="86"/>
+      <c r="D29" s="87"/>
+      <c r="E29" s="78"/>
+      <c r="F29" s="62"/>
+      <c r="G29" s="63"/>
+      <c r="H29" s="62"/>
+      <c r="I29" s="65"/>
+      <c r="J29" s="65"/>
+      <c r="K29" s="63"/>
+    </row>
+    <row r="30" spans="1:11" customFormat="1" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B30" s="83"/>
-      <c r="C30" s="22" t="s">
+      <c r="B31" s="25"/>
+      <c r="C31" s="91" t="s">
         <v>18</v>
       </c>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="22"/>
-      <c r="H30" s="22"/>
-      <c r="I30" s="22"/>
-      <c r="J30" s="22"/>
-      <c r="K30" s="22"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A31" s="83"/>
-      <c r="B31" s="83"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="22"/>
-      <c r="I31" s="22"/>
-      <c r="J31" s="22"/>
-      <c r="K31" s="22"/>
-    </row>
-    <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="84" t="s">
+      <c r="D31" s="91"/>
+      <c r="E31" s="91"/>
+      <c r="F31" s="91"/>
+      <c r="G31" s="91"/>
+      <c r="H31" s="91"/>
+      <c r="I31" s="91"/>
+      <c r="J31" s="91"/>
+      <c r="K31" s="91"/>
+    </row>
+    <row r="32" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="25"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="91"/>
+      <c r="D32" s="91"/>
+      <c r="E32" s="91"/>
+      <c r="F32" s="91"/>
+      <c r="G32" s="91"/>
+      <c r="H32" s="91"/>
+      <c r="I32" s="91"/>
+      <c r="J32" s="91"/>
+      <c r="K32" s="91"/>
+    </row>
+    <row r="33" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="B32" s="85"/>
-      <c r="C32" s="83"/>
-      <c r="D32" s="83"/>
-      <c r="E32" s="7" t="s">
+      <c r="B33" s="34"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F32" s="24" t="s">
+      <c r="F33" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="G33" s="22"/>
+      <c r="H33" s="90" t="s">
+        <v>44</v>
+      </c>
+      <c r="I33" s="90"/>
+      <c r="J33" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="K33" s="22"/>
+    </row>
+    <row r="34" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="35"/>
+      <c r="B34" s="36"/>
+      <c r="C34" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="40"/>
+      <c r="E34" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="G32" s="24"/>
-      <c r="H32" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="I32" s="21"/>
-      <c r="J32" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="K32" s="24"/>
-    </row>
-    <row r="33" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="86"/>
-      <c r="B33" s="87"/>
-      <c r="C33" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" s="91"/>
-      <c r="E33" s="11" t="s">
+      <c r="F34" s="49" t="s">
+        <v>32</v>
+      </c>
+      <c r="G34" s="47"/>
+      <c r="H34" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="I34" s="47"/>
+      <c r="J34" s="49" t="s">
+        <v>42</v>
+      </c>
+      <c r="K34" s="26"/>
+    </row>
+    <row r="35" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="37"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="D35" s="40"/>
+      <c r="E35" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="F33" s="19" t="s">
+      <c r="F35" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="G33" s="20"/>
-      <c r="H33" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="I33" s="20"/>
-      <c r="J33" s="19" t="s">
+      <c r="G35" s="47"/>
+      <c r="H35" s="49" t="s">
+        <v>46</v>
+      </c>
+      <c r="I35" s="47"/>
+      <c r="J35" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="K33" s="22"/>
-    </row>
-    <row r="34" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="88"/>
-      <c r="B34" s="89"/>
-      <c r="C34" s="90" t="s">
-        <v>21</v>
-      </c>
-      <c r="D34" s="91"/>
-      <c r="E34" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="F34" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="G34" s="20"/>
-      <c r="H34" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="I34" s="20"/>
-      <c r="J34" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="K34" s="22"/>
-    </row>
-    <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="24" t="s">
+      <c r="K35" s="26"/>
+    </row>
+    <row r="36" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="B35" s="83"/>
-      <c r="C35" s="24" t="s">
+      <c r="B36" s="25"/>
+      <c r="C36" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="D35" s="24"/>
-      <c r="E35" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="F35" s="25"/>
-      <c r="G35" s="24" t="s">
+      <c r="D36" s="22"/>
+      <c r="E36" s="89" t="s">
+        <v>40</v>
+      </c>
+      <c r="F36" s="89"/>
+      <c r="G36" s="22" t="s">
         <v>22</v>
-      </c>
-      <c r="H35" s="24"/>
-      <c r="I35" s="24"/>
-      <c r="J35" s="24"/>
-      <c r="K35" s="24"/>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A36" s="83"/>
-      <c r="B36" s="83"/>
-      <c r="C36" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="D36" s="22"/>
-      <c r="E36" s="23">
-        <v>0.99652777777777779</v>
-      </c>
-      <c r="F36" s="23"/>
-      <c r="G36" s="22" t="s">
-        <v>38</v>
       </c>
       <c r="H36" s="22"/>
       <c r="I36" s="22"/>
       <c r="J36" s="22"/>
       <c r="K36" s="22"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A37" s="83"/>
-      <c r="B37" s="83"/>
-      <c r="C37" s="22"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="22"/>
-      <c r="H37" s="22"/>
-      <c r="I37" s="22"/>
-      <c r="J37" s="22"/>
-      <c r="K37" s="22"/>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A38" s="24" t="s">
+    <row r="37" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="25"/>
+      <c r="B37" s="25"/>
+      <c r="C37" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="D37" s="26"/>
+      <c r="E37" s="88">
+        <v>0.99652777777777779</v>
+      </c>
+      <c r="F37" s="88"/>
+      <c r="G37" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="H37" s="26"/>
+      <c r="I37" s="26"/>
+      <c r="J37" s="26"/>
+      <c r="K37" s="26"/>
+    </row>
+    <row r="38" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="25"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="26"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="88"/>
+      <c r="F38" s="88"/>
+      <c r="G38" s="26"/>
+      <c r="H38" s="26"/>
+      <c r="I38" s="26"/>
+      <c r="J38" s="26"/>
+      <c r="K38" s="26"/>
+    </row>
+    <row r="39" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="B38" s="24"/>
-      <c r="C38" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="D38" s="27"/>
-      <c r="E38" s="27"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
-      <c r="H38" s="27"/>
-      <c r="I38" s="27"/>
-      <c r="J38" s="27"/>
-      <c r="K38" s="28"/>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A39" s="24"/>
-      <c r="B39" s="24"/>
-      <c r="C39" s="29" t="s">
+      <c r="B39" s="22"/>
+      <c r="C39" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="D39" s="28"/>
+      <c r="E39" s="28"/>
+      <c r="F39" s="28"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="28"/>
+      <c r="I39" s="28"/>
+      <c r="J39" s="28"/>
+      <c r="K39" s="29"/>
+    </row>
+    <row r="40" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="22"/>
+      <c r="B40" s="22"/>
+      <c r="C40" s="60" t="s">
         <v>28</v>
       </c>
-      <c r="D39" s="30"/>
-      <c r="E39" s="30"/>
-      <c r="F39" s="30"/>
-      <c r="G39" s="30"/>
-      <c r="H39" s="30"/>
-      <c r="I39" s="30"/>
-      <c r="J39" s="30"/>
-      <c r="K39" s="31"/>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A40" s="24"/>
-      <c r="B40" s="24"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="30"/>
-      <c r="G40" s="30"/>
-      <c r="H40" s="30"/>
-      <c r="I40" s="30"/>
-      <c r="J40" s="30"/>
-      <c r="K40" s="31"/>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A41" s="24"/>
-      <c r="B41" s="24"/>
-      <c r="C41" s="32"/>
-      <c r="D41" s="33"/>
-      <c r="E41" s="33"/>
-      <c r="F41" s="33"/>
-      <c r="G41" s="33"/>
-      <c r="H41" s="33"/>
-      <c r="I41" s="33"/>
-      <c r="J41" s="33"/>
-      <c r="K41" s="34"/>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A42" s="24" t="s">
+      <c r="D40" s="64"/>
+      <c r="E40" s="64"/>
+      <c r="F40" s="64"/>
+      <c r="G40" s="64"/>
+      <c r="H40" s="64"/>
+      <c r="I40" s="64"/>
+      <c r="J40" s="64"/>
+      <c r="K40" s="61"/>
+    </row>
+    <row r="41" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="22"/>
+      <c r="B41" s="22"/>
+      <c r="C41" s="60"/>
+      <c r="D41" s="64"/>
+      <c r="E41" s="64"/>
+      <c r="F41" s="64"/>
+      <c r="G41" s="64"/>
+      <c r="H41" s="64"/>
+      <c r="I41" s="64"/>
+      <c r="J41" s="64"/>
+      <c r="K41" s="61"/>
+    </row>
+    <row r="42" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="22"/>
+      <c r="B42" s="22"/>
+      <c r="C42" s="62"/>
+      <c r="D42" s="65"/>
+      <c r="E42" s="65"/>
+      <c r="F42" s="65"/>
+      <c r="G42" s="65"/>
+      <c r="H42" s="65"/>
+      <c r="I42" s="65"/>
+      <c r="J42" s="65"/>
+      <c r="K42" s="63"/>
+    </row>
+    <row r="43" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="B42" s="24"/>
-      <c r="C42" s="55" t="s">
+      <c r="B43" s="22"/>
+      <c r="C43" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="D42" s="62"/>
-      <c r="E42" s="62"/>
-      <c r="F42" s="62"/>
-      <c r="G42" s="62"/>
-      <c r="H42" s="62"/>
-      <c r="I42" s="62"/>
-      <c r="J42" s="62"/>
-      <c r="K42" s="56"/>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A43" s="24"/>
-      <c r="B43" s="24"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="30"/>
-      <c r="G43" s="30"/>
-      <c r="H43" s="30"/>
-      <c r="I43" s="30"/>
-      <c r="J43" s="30"/>
-      <c r="K43" s="31"/>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A44" s="24"/>
-      <c r="B44" s="24"/>
-      <c r="C44" s="29"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="30"/>
-      <c r="F44" s="30"/>
-      <c r="G44" s="30"/>
-      <c r="H44" s="30"/>
-      <c r="I44" s="30"/>
-      <c r="J44" s="30"/>
-      <c r="K44" s="31"/>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A45" s="24"/>
-      <c r="B45" s="24"/>
-      <c r="C45" s="32"/>
-      <c r="D45" s="33"/>
-      <c r="E45" s="33"/>
-      <c r="F45" s="33"/>
-      <c r="G45" s="33"/>
-      <c r="H45" s="33"/>
-      <c r="I45" s="33"/>
-      <c r="J45" s="33"/>
-      <c r="K45" s="34"/>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A46" s="24" t="s">
+      <c r="D43" s="28"/>
+      <c r="E43" s="28"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="28"/>
+      <c r="I43" s="28"/>
+      <c r="J43" s="28"/>
+      <c r="K43" s="29"/>
+    </row>
+    <row r="44" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="22"/>
+      <c r="B44" s="22"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="20"/>
+      <c r="G44" s="20"/>
+      <c r="H44" s="20"/>
+      <c r="I44" s="20"/>
+      <c r="J44" s="20"/>
+      <c r="K44" s="21"/>
+    </row>
+    <row r="45" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="22"/>
+      <c r="B45" s="22"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="20"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="20"/>
+      <c r="H45" s="20"/>
+      <c r="I45" s="20"/>
+      <c r="J45" s="20"/>
+      <c r="K45" s="21"/>
+    </row>
+    <row r="46" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="22"/>
+      <c r="B46" s="22"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="31"/>
+      <c r="E46" s="31"/>
+      <c r="F46" s="31"/>
+      <c r="G46" s="31"/>
+      <c r="H46" s="31"/>
+      <c r="I46" s="31"/>
+      <c r="J46" s="31"/>
+      <c r="K46" s="32"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A47" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="B46" s="24"/>
-      <c r="C46" s="81" t="s">
-        <v>29</v>
-      </c>
-      <c r="D46" s="82"/>
-      <c r="E46" s="82"/>
-      <c r="F46" s="82"/>
-      <c r="G46" s="82"/>
-      <c r="H46" s="82"/>
-      <c r="I46" s="82"/>
-      <c r="J46" s="82"/>
-      <c r="K46" s="82"/>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A47" s="24"/>
-      <c r="B47" s="24"/>
-      <c r="C47" s="82"/>
-      <c r="D47" s="82"/>
-      <c r="E47" s="82"/>
-      <c r="F47" s="82"/>
-      <c r="G47" s="82"/>
-      <c r="H47" s="82"/>
-      <c r="I47" s="82"/>
-      <c r="J47" s="82"/>
-      <c r="K47" s="82"/>
+      <c r="B47" s="22"/>
+      <c r="C47" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="D47" s="24"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="24"/>
+      <c r="H47" s="24"/>
+      <c r="I47" s="24"/>
+      <c r="J47" s="24"/>
+      <c r="K47" s="24"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A48" s="22"/>
+      <c r="B48" s="22"/>
+      <c r="C48" s="24"/>
+      <c r="D48" s="24"/>
+      <c r="E48" s="24"/>
+      <c r="F48" s="24"/>
+      <c r="G48" s="24"/>
+      <c r="H48" s="24"/>
+      <c r="I48" s="24"/>
+      <c r="J48" s="24"/>
+      <c r="K48" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="C44:K44"/>
-    <mergeCell ref="A46:B47"/>
-    <mergeCell ref="C46:K47"/>
-    <mergeCell ref="A30:B31"/>
-    <mergeCell ref="C30:K31"/>
-    <mergeCell ref="A42:B45"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="C37:D38"/>
+    <mergeCell ref="E37:F38"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="G36:K36"/>
+    <mergeCell ref="G37:K38"/>
+    <mergeCell ref="A39:B42"/>
+    <mergeCell ref="C39:K39"/>
+    <mergeCell ref="C40:K40"/>
+    <mergeCell ref="C41:K41"/>
     <mergeCell ref="C42:K42"/>
-    <mergeCell ref="C43:K43"/>
-    <mergeCell ref="C45:K45"/>
-    <mergeCell ref="A35:B37"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="A32:B34"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B29"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E12:E17"/>
+    <mergeCell ref="E18:E23"/>
+    <mergeCell ref="E24:E29"/>
+    <mergeCell ref="C12:D14"/>
+    <mergeCell ref="C15:D17"/>
+    <mergeCell ref="C18:D20"/>
+    <mergeCell ref="C21:D23"/>
+    <mergeCell ref="C24:D26"/>
+    <mergeCell ref="C27:D29"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F18:G23"/>
+    <mergeCell ref="F24:G29"/>
+    <mergeCell ref="H12:K14"/>
+    <mergeCell ref="H15:K17"/>
+    <mergeCell ref="H18:K20"/>
+    <mergeCell ref="H21:K23"/>
+    <mergeCell ref="H24:K26"/>
+    <mergeCell ref="H27:K29"/>
+    <mergeCell ref="H11:K11"/>
+    <mergeCell ref="F12:G17"/>
     <mergeCell ref="A9:K9"/>
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="A3:K3"/>
@@ -1838,48 +1864,24 @@
     <mergeCell ref="H7:K7"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:E2"/>
-    <mergeCell ref="F12:G17"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F18:G23"/>
-    <mergeCell ref="F24:G29"/>
-    <mergeCell ref="H12:K14"/>
-    <mergeCell ref="H15:K17"/>
-    <mergeCell ref="H18:K20"/>
-    <mergeCell ref="H21:K23"/>
-    <mergeCell ref="H24:K26"/>
-    <mergeCell ref="H27:K29"/>
-    <mergeCell ref="H11:K11"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B29"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E12:E17"/>
-    <mergeCell ref="E18:E23"/>
-    <mergeCell ref="E24:E29"/>
-    <mergeCell ref="C12:D14"/>
-    <mergeCell ref="C15:D17"/>
-    <mergeCell ref="C18:D20"/>
-    <mergeCell ref="C21:D23"/>
-    <mergeCell ref="C24:D26"/>
-    <mergeCell ref="C27:D29"/>
-    <mergeCell ref="A38:B41"/>
-    <mergeCell ref="C38:K38"/>
-    <mergeCell ref="C39:K39"/>
-    <mergeCell ref="C40:K40"/>
-    <mergeCell ref="C41:K41"/>
-    <mergeCell ref="C36:D37"/>
-    <mergeCell ref="E36:F37"/>
+    <mergeCell ref="C45:K45"/>
+    <mergeCell ref="A47:B48"/>
+    <mergeCell ref="C47:K48"/>
+    <mergeCell ref="A31:B32"/>
+    <mergeCell ref="C31:K32"/>
+    <mergeCell ref="A43:B46"/>
+    <mergeCell ref="C43:K43"/>
+    <mergeCell ref="C44:K44"/>
+    <mergeCell ref="C46:K46"/>
+    <mergeCell ref="A36:B38"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="A33:B35"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="C34:D34"/>
     <mergeCell ref="C35:D35"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="G35:K35"/>
-    <mergeCell ref="G36:K37"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="C33:D33"/>
   </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.25" footer="0.25"/>
   <pageSetup paperSize="9" fitToWidth="0" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>

--- a/Template/Voucher Template.xlsx
+++ b/Template/Voucher Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Smart Travel PC\Desktop\Vouchers Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC047EC8-AB16-4218-A569-6B5882E2D2B6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71887FCA-7627-42B4-B928-58DAA0508DAE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="675" windowWidth="19935" windowHeight="15525" xr2:uid="{46FCF62E-0F38-40EF-B40B-6239A54C7BFA}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="19935" windowHeight="15525" xr2:uid="{46FCF62E-0F38-40EF-B40B-6239A54C7BFA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="49">
   <si>
     <t>TO:</t>
   </si>
@@ -169,6 +169,9 @@
   </si>
   <si>
     <t>*** It will be subject to change based on the local situation ***</t>
+  </si>
+  <si>
+    <t>To</t>
   </si>
 </sst>
 </file>
@@ -440,7 +443,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -488,6 +491,30 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -509,7 +536,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -668,32 +695,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -702,9 +711,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -728,23 +734,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19051</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>19049</xdr:rowOff>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>104775</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>866775</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>723900</xdr:rowOff>
+      <xdr:rowOff>695325</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
+        <xdr:cNvPr id="4" name="Picture 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0BDFC6A-3B55-4B5E-ABF3-1BFC47E49B9C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE603332-4781-4BA8-8741-D097C8C0E67B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -752,21 +758,22 @@
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:srcRect l="14562" t="38950" r="24164" b="43105"/>
-        <a:stretch/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1752600" y="19049"/>
-          <a:ext cx="2924175" cy="704851"/>
+          <a:off x="19051" y="95250"/>
+          <a:ext cx="6638924" cy="600075"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1104,37 +1111,37 @@
       <c r="K1" s="2"/>
     </row>
     <row r="2" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="54" t="s">
+      <c r="A2" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="58"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="66"/>
       <c r="F2" s="13"/>
       <c r="G2" s="14"/>
       <c r="H2" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="41"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="43"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="51"/>
       <c r="N2" s="2"/>
     </row>
     <row r="3" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="46"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="54"/>
       <c r="N3" s="2"/>
     </row>
     <row r="4" spans="1:14" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1155,64 +1162,64 @@
       <c r="A5" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="50" t="s">
+      <c r="B5" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="52" t="s">
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="53"/>
-      <c r="H5" s="47" t="s">
+      <c r="G5" s="61"/>
+      <c r="H5" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
-      <c r="K5" s="49"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="56"/>
+      <c r="K5" s="57"/>
     </row>
     <row r="6" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="50" t="s">
+      <c r="B6" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="52" t="s">
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="53"/>
-      <c r="H6" s="47" t="s">
+      <c r="G6" s="61"/>
+      <c r="H6" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="49"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="56"/>
+      <c r="K6" s="57"/>
     </row>
     <row r="7" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="51" t="s">
+      <c r="B7" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="51"/>
-      <c r="F7" s="52" t="s">
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="53"/>
-      <c r="H7" s="47" t="s">
+      <c r="G7" s="61"/>
+      <c r="H7" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="49"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="56"/>
+      <c r="K7" s="57"/>
     </row>
     <row r="8" spans="1:14" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
@@ -1228,19 +1235,19 @@
       <c r="K8" s="2"/>
     </row>
     <row r="9" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="22"/>
-      <c r="K9" s="22"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="30"/>
     </row>
     <row r="10" spans="1:14" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
@@ -1256,559 +1263,569 @@
       <c r="K10" s="2"/>
     </row>
     <row r="11" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="44"/>
-      <c r="B11" s="69"/>
-      <c r="C11" s="66" t="s">
+      <c r="A11" s="52"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="74" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="68"/>
+      <c r="D11" s="76"/>
       <c r="E11" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="59" t="s">
+      <c r="F11" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="G11" s="59"/>
-      <c r="H11" s="66" t="s">
+      <c r="G11" s="67"/>
+      <c r="H11" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="I11" s="67"/>
-      <c r="J11" s="67"/>
-      <c r="K11" s="68"/>
+      <c r="I11" s="75"/>
+      <c r="J11" s="75"/>
+      <c r="K11" s="76"/>
     </row>
     <row r="12" spans="1:14" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="70"/>
-      <c r="B12" s="71"/>
-      <c r="C12" s="79"/>
-      <c r="D12" s="80"/>
-      <c r="E12" s="76"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="28"/>
-      <c r="J12" s="28"/>
-      <c r="K12" s="29"/>
+      <c r="A12" s="78"/>
+      <c r="B12" s="79"/>
+      <c r="C12" s="19">
+        <v>45855</v>
+      </c>
+      <c r="D12" s="20"/>
+      <c r="E12" s="84"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="37"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="36"/>
+      <c r="J12" s="36"/>
+      <c r="K12" s="37"/>
     </row>
     <row r="13" spans="1:14" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="72"/>
-      <c r="B13" s="73"/>
-      <c r="C13" s="81"/>
-      <c r="D13" s="82"/>
-      <c r="E13" s="77"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="61"/>
-      <c r="H13" s="60"/>
-      <c r="I13" s="64"/>
-      <c r="J13" s="64"/>
-      <c r="K13" s="61"/>
-    </row>
-    <row r="14" spans="1:14" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="72"/>
-      <c r="B14" s="73"/>
-      <c r="C14" s="81"/>
-      <c r="D14" s="82"/>
-      <c r="E14" s="77"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="61"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="65"/>
-      <c r="J14" s="65"/>
-      <c r="K14" s="63"/>
-    </row>
-    <row r="15" spans="1:14" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="72"/>
-      <c r="B15" s="73"/>
-      <c r="C15" s="83"/>
-      <c r="D15" s="84"/>
-      <c r="E15" s="77"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="61"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="28"/>
-      <c r="J15" s="28"/>
-      <c r="K15" s="29"/>
+      <c r="A13" s="80"/>
+      <c r="B13" s="81"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="85"/>
+      <c r="F13" s="68"/>
+      <c r="G13" s="69"/>
+      <c r="H13" s="68"/>
+      <c r="I13" s="72"/>
+      <c r="J13" s="72"/>
+      <c r="K13" s="69"/>
+    </row>
+    <row r="14" spans="1:14" s="4" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="80"/>
+      <c r="B14" s="81"/>
+      <c r="C14" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="24"/>
+      <c r="E14" s="85"/>
+      <c r="F14" s="68"/>
+      <c r="G14" s="69"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="73"/>
+      <c r="J14" s="73"/>
+      <c r="K14" s="71"/>
+    </row>
+    <row r="15" spans="1:14" s="4" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="80"/>
+      <c r="B15" s="81"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="85"/>
+      <c r="F15" s="68"/>
+      <c r="G15" s="69"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="36"/>
+      <c r="J15" s="36"/>
+      <c r="K15" s="37"/>
     </row>
     <row r="16" spans="1:14" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="72"/>
-      <c r="B16" s="73"/>
-      <c r="C16" s="85"/>
-      <c r="D16" s="84"/>
-      <c r="E16" s="77"/>
-      <c r="F16" s="60"/>
-      <c r="G16" s="61"/>
-      <c r="H16" s="60"/>
-      <c r="I16" s="64"/>
-      <c r="J16" s="64"/>
-      <c r="K16" s="61"/>
+      <c r="A16" s="80"/>
+      <c r="B16" s="81"/>
+      <c r="C16" s="21">
+        <v>45855</v>
+      </c>
+      <c r="D16" s="22"/>
+      <c r="E16" s="85"/>
+      <c r="F16" s="68"/>
+      <c r="G16" s="69"/>
+      <c r="H16" s="68"/>
+      <c r="I16" s="72"/>
+      <c r="J16" s="72"/>
+      <c r="K16" s="69"/>
     </row>
     <row r="17" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="72"/>
-      <c r="B17" s="73"/>
-      <c r="C17" s="86"/>
-      <c r="D17" s="87"/>
-      <c r="E17" s="78"/>
-      <c r="F17" s="62"/>
-      <c r="G17" s="63"/>
-      <c r="H17" s="62"/>
-      <c r="I17" s="65"/>
-      <c r="J17" s="65"/>
-      <c r="K17" s="63"/>
+      <c r="A17" s="80"/>
+      <c r="B17" s="81"/>
+      <c r="C17" s="87"/>
+      <c r="D17" s="88"/>
+      <c r="E17" s="86"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="70"/>
+      <c r="I17" s="73"/>
+      <c r="J17" s="73"/>
+      <c r="K17" s="71"/>
     </row>
     <row r="18" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="72"/>
-      <c r="B18" s="73"/>
-      <c r="C18" s="79"/>
-      <c r="D18" s="80"/>
-      <c r="E18" s="76"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="27"/>
-      <c r="I18" s="28"/>
-      <c r="J18" s="28"/>
-      <c r="K18" s="29"/>
+      <c r="A18" s="80"/>
+      <c r="B18" s="81"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="84"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="36"/>
+      <c r="J18" s="36"/>
+      <c r="K18" s="37"/>
     </row>
     <row r="19" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="72"/>
-      <c r="B19" s="73"/>
-      <c r="C19" s="81"/>
-      <c r="D19" s="82"/>
-      <c r="E19" s="77"/>
-      <c r="F19" s="60"/>
-      <c r="G19" s="61"/>
-      <c r="H19" s="60"/>
-      <c r="I19" s="64"/>
-      <c r="J19" s="64"/>
-      <c r="K19" s="61"/>
-    </row>
-    <row r="20" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="72"/>
-      <c r="B20" s="73"/>
-      <c r="C20" s="81"/>
-      <c r="D20" s="82"/>
-      <c r="E20" s="77"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="61"/>
-      <c r="H20" s="62"/>
-      <c r="I20" s="65"/>
-      <c r="J20" s="65"/>
-      <c r="K20" s="63"/>
-    </row>
-    <row r="21" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="72"/>
-      <c r="B21" s="73"/>
-      <c r="C21" s="83"/>
-      <c r="D21" s="84"/>
-      <c r="E21" s="77"/>
-      <c r="F21" s="60"/>
-      <c r="G21" s="61"/>
-      <c r="H21" s="27"/>
-      <c r="I21" s="28"/>
-      <c r="J21" s="28"/>
-      <c r="K21" s="29"/>
+      <c r="A19" s="80"/>
+      <c r="B19" s="81"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="85"/>
+      <c r="F19" s="68"/>
+      <c r="G19" s="69"/>
+      <c r="H19" s="68"/>
+      <c r="I19" s="72"/>
+      <c r="J19" s="72"/>
+      <c r="K19" s="69"/>
+    </row>
+    <row r="20" spans="1:11" s="4" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="80"/>
+      <c r="B20" s="81"/>
+      <c r="C20" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="24"/>
+      <c r="E20" s="85"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="69"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="73"/>
+      <c r="J20" s="73"/>
+      <c r="K20" s="71"/>
+    </row>
+    <row r="21" spans="1:11" s="4" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="80"/>
+      <c r="B21" s="81"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="85"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="69"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="36"/>
+      <c r="J21" s="36"/>
+      <c r="K21" s="37"/>
     </row>
     <row r="22" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="72"/>
-      <c r="B22" s="73"/>
-      <c r="C22" s="85"/>
-      <c r="D22" s="84"/>
-      <c r="E22" s="77"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="61"/>
-      <c r="H22" s="60"/>
-      <c r="I22" s="64"/>
-      <c r="J22" s="64"/>
-      <c r="K22" s="61"/>
+      <c r="A22" s="80"/>
+      <c r="B22" s="81"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="85"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="69"/>
+      <c r="H22" s="68"/>
+      <c r="I22" s="72"/>
+      <c r="J22" s="72"/>
+      <c r="K22" s="69"/>
     </row>
     <row r="23" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="72"/>
-      <c r="B23" s="73"/>
-      <c r="C23" s="86"/>
-      <c r="D23" s="87"/>
-      <c r="E23" s="78"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="63"/>
-      <c r="H23" s="62"/>
-      <c r="I23" s="65"/>
-      <c r="J23" s="65"/>
-      <c r="K23" s="63"/>
+      <c r="A23" s="80"/>
+      <c r="B23" s="81"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="86"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="73"/>
+      <c r="J23" s="73"/>
+      <c r="K23" s="71"/>
     </row>
     <row r="24" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="72"/>
-      <c r="B24" s="73"/>
-      <c r="C24" s="79"/>
-      <c r="D24" s="80"/>
-      <c r="E24" s="76"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="27"/>
-      <c r="I24" s="28"/>
-      <c r="J24" s="28"/>
-      <c r="K24" s="29"/>
+      <c r="A24" s="80"/>
+      <c r="B24" s="81"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="84"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="37"/>
+      <c r="H24" s="35"/>
+      <c r="I24" s="36"/>
+      <c r="J24" s="36"/>
+      <c r="K24" s="37"/>
     </row>
     <row r="25" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="72"/>
-      <c r="B25" s="73"/>
-      <c r="C25" s="81"/>
-      <c r="D25" s="82"/>
-      <c r="E25" s="77"/>
-      <c r="F25" s="60"/>
-      <c r="G25" s="61"/>
-      <c r="H25" s="60"/>
-      <c r="I25" s="64"/>
-      <c r="J25" s="64"/>
-      <c r="K25" s="61"/>
-    </row>
-    <row r="26" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="72"/>
-      <c r="B26" s="73"/>
-      <c r="C26" s="81"/>
-      <c r="D26" s="82"/>
-      <c r="E26" s="77"/>
-      <c r="F26" s="60"/>
-      <c r="G26" s="61"/>
-      <c r="H26" s="62"/>
-      <c r="I26" s="65"/>
-      <c r="J26" s="65"/>
-      <c r="K26" s="63"/>
-    </row>
-    <row r="27" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="72"/>
-      <c r="B27" s="73"/>
-      <c r="C27" s="83"/>
-      <c r="D27" s="84"/>
-      <c r="E27" s="77"/>
-      <c r="F27" s="60"/>
-      <c r="G27" s="61"/>
-      <c r="H27" s="27"/>
-      <c r="I27" s="28"/>
-      <c r="J27" s="28"/>
-      <c r="K27" s="29"/>
+      <c r="A25" s="80"/>
+      <c r="B25" s="81"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="85"/>
+      <c r="F25" s="68"/>
+      <c r="G25" s="69"/>
+      <c r="H25" s="68"/>
+      <c r="I25" s="72"/>
+      <c r="J25" s="72"/>
+      <c r="K25" s="69"/>
+    </row>
+    <row r="26" spans="1:11" s="4" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="80"/>
+      <c r="B26" s="81"/>
+      <c r="C26" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" s="24"/>
+      <c r="E26" s="85"/>
+      <c r="F26" s="68"/>
+      <c r="G26" s="69"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="73"/>
+      <c r="J26" s="73"/>
+      <c r="K26" s="71"/>
+    </row>
+    <row r="27" spans="1:11" s="4" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="80"/>
+      <c r="B27" s="81"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="85"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="69"/>
+      <c r="H27" s="35"/>
+      <c r="I27" s="36"/>
+      <c r="J27" s="36"/>
+      <c r="K27" s="37"/>
     </row>
     <row r="28" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="72"/>
-      <c r="B28" s="73"/>
-      <c r="C28" s="85"/>
-      <c r="D28" s="84"/>
-      <c r="E28" s="77"/>
-      <c r="F28" s="60"/>
-      <c r="G28" s="61"/>
-      <c r="H28" s="60"/>
-      <c r="I28" s="64"/>
-      <c r="J28" s="64"/>
-      <c r="K28" s="61"/>
+      <c r="A28" s="80"/>
+      <c r="B28" s="81"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="85"/>
+      <c r="F28" s="68"/>
+      <c r="G28" s="69"/>
+      <c r="H28" s="68"/>
+      <c r="I28" s="72"/>
+      <c r="J28" s="72"/>
+      <c r="K28" s="69"/>
     </row>
     <row r="29" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="74"/>
-      <c r="B29" s="75"/>
-      <c r="C29" s="86"/>
-      <c r="D29" s="87"/>
-      <c r="E29" s="78"/>
-      <c r="F29" s="62"/>
-      <c r="G29" s="63"/>
-      <c r="H29" s="62"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="65"/>
-      <c r="K29" s="63"/>
+      <c r="A29" s="82"/>
+      <c r="B29" s="83"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="86"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="73"/>
+      <c r="J29" s="73"/>
+      <c r="K29" s="71"/>
     </row>
     <row r="30" spans="1:11" customFormat="1" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="22" t="s">
+      <c r="A31" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B31" s="25"/>
-      <c r="C31" s="91" t="s">
+      <c r="B31" s="33"/>
+      <c r="C31" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="D31" s="91"/>
-      <c r="E31" s="91"/>
-      <c r="F31" s="91"/>
-      <c r="G31" s="91"/>
-      <c r="H31" s="91"/>
-      <c r="I31" s="91"/>
-      <c r="J31" s="91"/>
-      <c r="K31" s="91"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="34"/>
+      <c r="G31" s="34"/>
+      <c r="H31" s="34"/>
+      <c r="I31" s="34"/>
+      <c r="J31" s="34"/>
+      <c r="K31" s="34"/>
     </row>
     <row r="32" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="25"/>
-      <c r="B32" s="25"/>
-      <c r="C32" s="91"/>
-      <c r="D32" s="91"/>
-      <c r="E32" s="91"/>
-      <c r="F32" s="91"/>
-      <c r="G32" s="91"/>
-      <c r="H32" s="91"/>
-      <c r="I32" s="91"/>
-      <c r="J32" s="91"/>
-      <c r="K32" s="91"/>
+      <c r="A32" s="33"/>
+      <c r="B32" s="33"/>
+      <c r="C32" s="34"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="34"/>
+      <c r="I32" s="34"/>
+      <c r="J32" s="34"/>
+      <c r="K32" s="34"/>
     </row>
     <row r="33" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="33" t="s">
+      <c r="A33" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="B33" s="34"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="25"/>
+      <c r="B33" s="42"/>
+      <c r="C33" s="33"/>
+      <c r="D33" s="33"/>
       <c r="E33" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F33" s="22" t="s">
+      <c r="F33" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="G33" s="22"/>
-      <c r="H33" s="90" t="s">
+      <c r="G33" s="30"/>
+      <c r="H33" s="92" t="s">
         <v>44</v>
       </c>
-      <c r="I33" s="90"/>
-      <c r="J33" s="22" t="s">
+      <c r="I33" s="92"/>
+      <c r="J33" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="K33" s="22"/>
+      <c r="K33" s="30"/>
     </row>
     <row r="34" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="35"/>
-      <c r="B34" s="36"/>
-      <c r="C34" s="39" t="s">
+      <c r="A34" s="43"/>
+      <c r="B34" s="44"/>
+      <c r="C34" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="D34" s="40"/>
+      <c r="D34" s="48"/>
       <c r="E34" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="F34" s="49" t="s">
+      <c r="F34" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="G34" s="47"/>
-      <c r="H34" s="49" t="s">
+      <c r="G34" s="55"/>
+      <c r="H34" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="I34" s="47"/>
-      <c r="J34" s="49" t="s">
+      <c r="I34" s="55"/>
+      <c r="J34" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="K34" s="26"/>
+      <c r="K34" s="89"/>
     </row>
     <row r="35" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="37"/>
-      <c r="B35" s="38"/>
-      <c r="C35" s="39" t="s">
+      <c r="A35" s="45"/>
+      <c r="B35" s="46"/>
+      <c r="C35" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="D35" s="40"/>
+      <c r="D35" s="48"/>
       <c r="E35" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="F35" s="49" t="s">
+      <c r="F35" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="G35" s="47"/>
-      <c r="H35" s="49" t="s">
+      <c r="G35" s="55"/>
+      <c r="H35" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="I35" s="47"/>
-      <c r="J35" s="49" t="s">
+      <c r="I35" s="55"/>
+      <c r="J35" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="K35" s="26"/>
+      <c r="K35" s="89"/>
     </row>
     <row r="36" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="22" t="s">
+      <c r="A36" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="B36" s="25"/>
-      <c r="C36" s="22" t="s">
+      <c r="B36" s="33"/>
+      <c r="C36" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="D36" s="22"/>
-      <c r="E36" s="89" t="s">
+      <c r="D36" s="30"/>
+      <c r="E36" s="91" t="s">
         <v>40</v>
       </c>
-      <c r="F36" s="89"/>
-      <c r="G36" s="22" t="s">
+      <c r="F36" s="91"/>
+      <c r="G36" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="H36" s="22"/>
-      <c r="I36" s="22"/>
-      <c r="J36" s="22"/>
-      <c r="K36" s="22"/>
+      <c r="H36" s="30"/>
+      <c r="I36" s="30"/>
+      <c r="J36" s="30"/>
+      <c r="K36" s="30"/>
     </row>
     <row r="37" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="25"/>
-      <c r="B37" s="25"/>
-      <c r="C37" s="26" t="s">
+      <c r="A37" s="33"/>
+      <c r="B37" s="33"/>
+      <c r="C37" s="89" t="s">
         <v>36</v>
       </c>
-      <c r="D37" s="26"/>
-      <c r="E37" s="88">
+      <c r="D37" s="89"/>
+      <c r="E37" s="90">
         <v>0.99652777777777779</v>
       </c>
-      <c r="F37" s="88"/>
-      <c r="G37" s="26" t="s">
+      <c r="F37" s="90"/>
+      <c r="G37" s="89" t="s">
         <v>37</v>
       </c>
-      <c r="H37" s="26"/>
-      <c r="I37" s="26"/>
-      <c r="J37" s="26"/>
-      <c r="K37" s="26"/>
+      <c r="H37" s="89"/>
+      <c r="I37" s="89"/>
+      <c r="J37" s="89"/>
+      <c r="K37" s="89"/>
     </row>
     <row r="38" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="25"/>
-      <c r="B38" s="25"/>
-      <c r="C38" s="26"/>
-      <c r="D38" s="26"/>
-      <c r="E38" s="88"/>
-      <c r="F38" s="88"/>
-      <c r="G38" s="26"/>
-      <c r="H38" s="26"/>
-      <c r="I38" s="26"/>
-      <c r="J38" s="26"/>
-      <c r="K38" s="26"/>
+      <c r="A38" s="33"/>
+      <c r="B38" s="33"/>
+      <c r="C38" s="89"/>
+      <c r="D38" s="89"/>
+      <c r="E38" s="90"/>
+      <c r="F38" s="90"/>
+      <c r="G38" s="89"/>
+      <c r="H38" s="89"/>
+      <c r="I38" s="89"/>
+      <c r="J38" s="89"/>
+      <c r="K38" s="89"/>
     </row>
     <row r="39" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="22" t="s">
+      <c r="A39" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="B39" s="22"/>
-      <c r="C39" s="27" t="s">
+      <c r="B39" s="30"/>
+      <c r="C39" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="D39" s="28"/>
-      <c r="E39" s="28"/>
-      <c r="F39" s="28"/>
-      <c r="G39" s="28"/>
-      <c r="H39" s="28"/>
-      <c r="I39" s="28"/>
-      <c r="J39" s="28"/>
-      <c r="K39" s="29"/>
+      <c r="D39" s="36"/>
+      <c r="E39" s="36"/>
+      <c r="F39" s="36"/>
+      <c r="G39" s="36"/>
+      <c r="H39" s="36"/>
+      <c r="I39" s="36"/>
+      <c r="J39" s="36"/>
+      <c r="K39" s="37"/>
     </row>
     <row r="40" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="22"/>
-      <c r="B40" s="22"/>
-      <c r="C40" s="60" t="s">
+      <c r="A40" s="30"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="D40" s="64"/>
-      <c r="E40" s="64"/>
-      <c r="F40" s="64"/>
-      <c r="G40" s="64"/>
-      <c r="H40" s="64"/>
-      <c r="I40" s="64"/>
-      <c r="J40" s="64"/>
-      <c r="K40" s="61"/>
+      <c r="D40" s="72"/>
+      <c r="E40" s="72"/>
+      <c r="F40" s="72"/>
+      <c r="G40" s="72"/>
+      <c r="H40" s="72"/>
+      <c r="I40" s="72"/>
+      <c r="J40" s="72"/>
+      <c r="K40" s="69"/>
     </row>
     <row r="41" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="22"/>
-      <c r="B41" s="22"/>
-      <c r="C41" s="60"/>
-      <c r="D41" s="64"/>
-      <c r="E41" s="64"/>
-      <c r="F41" s="64"/>
-      <c r="G41" s="64"/>
-      <c r="H41" s="64"/>
-      <c r="I41" s="64"/>
-      <c r="J41" s="64"/>
-      <c r="K41" s="61"/>
+      <c r="A41" s="30"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="68"/>
+      <c r="D41" s="72"/>
+      <c r="E41" s="72"/>
+      <c r="F41" s="72"/>
+      <c r="G41" s="72"/>
+      <c r="H41" s="72"/>
+      <c r="I41" s="72"/>
+      <c r="J41" s="72"/>
+      <c r="K41" s="69"/>
     </row>
     <row r="42" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="22"/>
-      <c r="B42" s="22"/>
-      <c r="C42" s="62"/>
-      <c r="D42" s="65"/>
-      <c r="E42" s="65"/>
-      <c r="F42" s="65"/>
-      <c r="G42" s="65"/>
-      <c r="H42" s="65"/>
-      <c r="I42" s="65"/>
-      <c r="J42" s="65"/>
-      <c r="K42" s="63"/>
+      <c r="A42" s="30"/>
+      <c r="B42" s="30"/>
+      <c r="C42" s="70"/>
+      <c r="D42" s="73"/>
+      <c r="E42" s="73"/>
+      <c r="F42" s="73"/>
+      <c r="G42" s="73"/>
+      <c r="H42" s="73"/>
+      <c r="I42" s="73"/>
+      <c r="J42" s="73"/>
+      <c r="K42" s="71"/>
     </row>
     <row r="43" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="22" t="s">
+      <c r="A43" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="B43" s="22"/>
-      <c r="C43" s="27" t="s">
+      <c r="B43" s="30"/>
+      <c r="C43" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="D43" s="28"/>
-      <c r="E43" s="28"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="28"/>
-      <c r="H43" s="28"/>
-      <c r="I43" s="28"/>
-      <c r="J43" s="28"/>
-      <c r="K43" s="29"/>
+      <c r="D43" s="36"/>
+      <c r="E43" s="36"/>
+      <c r="F43" s="36"/>
+      <c r="G43" s="36"/>
+      <c r="H43" s="36"/>
+      <c r="I43" s="36"/>
+      <c r="J43" s="36"/>
+      <c r="K43" s="37"/>
     </row>
     <row r="44" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="22"/>
-      <c r="B44" s="22"/>
-      <c r="C44" s="19"/>
-      <c r="D44" s="20"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="20"/>
-      <c r="G44" s="20"/>
-      <c r="H44" s="20"/>
-      <c r="I44" s="20"/>
-      <c r="J44" s="20"/>
-      <c r="K44" s="21"/>
+      <c r="A44" s="30"/>
+      <c r="B44" s="30"/>
+      <c r="C44" s="27"/>
+      <c r="D44" s="28"/>
+      <c r="E44" s="28"/>
+      <c r="F44" s="28"/>
+      <c r="G44" s="28"/>
+      <c r="H44" s="28"/>
+      <c r="I44" s="28"/>
+      <c r="J44" s="28"/>
+      <c r="K44" s="29"/>
     </row>
     <row r="45" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="22"/>
-      <c r="B45" s="22"/>
-      <c r="C45" s="19"/>
-      <c r="D45" s="20"/>
-      <c r="E45" s="20"/>
-      <c r="F45" s="20"/>
-      <c r="G45" s="20"/>
-      <c r="H45" s="20"/>
-      <c r="I45" s="20"/>
-      <c r="J45" s="20"/>
-      <c r="K45" s="21"/>
+      <c r="A45" s="30"/>
+      <c r="B45" s="30"/>
+      <c r="C45" s="27"/>
+      <c r="D45" s="28"/>
+      <c r="E45" s="28"/>
+      <c r="F45" s="28"/>
+      <c r="G45" s="28"/>
+      <c r="H45" s="28"/>
+      <c r="I45" s="28"/>
+      <c r="J45" s="28"/>
+      <c r="K45" s="29"/>
     </row>
     <row r="46" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="22"/>
-      <c r="B46" s="22"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="31"/>
-      <c r="E46" s="31"/>
-      <c r="F46" s="31"/>
-      <c r="G46" s="31"/>
-      <c r="H46" s="31"/>
-      <c r="I46" s="31"/>
-      <c r="J46" s="31"/>
-      <c r="K46" s="32"/>
+      <c r="A46" s="30"/>
+      <c r="B46" s="30"/>
+      <c r="C46" s="38"/>
+      <c r="D46" s="39"/>
+      <c r="E46" s="39"/>
+      <c r="F46" s="39"/>
+      <c r="G46" s="39"/>
+      <c r="H46" s="39"/>
+      <c r="I46" s="39"/>
+      <c r="J46" s="39"/>
+      <c r="K46" s="40"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A47" s="22" t="s">
+      <c r="A47" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="B47" s="22"/>
-      <c r="C47" s="23" t="s">
+      <c r="B47" s="30"/>
+      <c r="C47" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="D47" s="24"/>
-      <c r="E47" s="24"/>
-      <c r="F47" s="24"/>
-      <c r="G47" s="24"/>
-      <c r="H47" s="24"/>
-      <c r="I47" s="24"/>
-      <c r="J47" s="24"/>
-      <c r="K47" s="24"/>
+      <c r="D47" s="32"/>
+      <c r="E47" s="32"/>
+      <c r="F47" s="32"/>
+      <c r="G47" s="32"/>
+      <c r="H47" s="32"/>
+      <c r="I47" s="32"/>
+      <c r="J47" s="32"/>
+      <c r="K47" s="32"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A48" s="22"/>
-      <c r="B48" s="22"/>
-      <c r="C48" s="24"/>
-      <c r="D48" s="24"/>
-      <c r="E48" s="24"/>
-      <c r="F48" s="24"/>
-      <c r="G48" s="24"/>
-      <c r="H48" s="24"/>
-      <c r="I48" s="24"/>
-      <c r="J48" s="24"/>
-      <c r="K48" s="24"/>
+      <c r="A48" s="30"/>
+      <c r="B48" s="30"/>
+      <c r="C48" s="32"/>
+      <c r="D48" s="32"/>
+      <c r="E48" s="32"/>
+      <c r="F48" s="32"/>
+      <c r="G48" s="32"/>
+      <c r="H48" s="32"/>
+      <c r="I48" s="32"/>
+      <c r="J48" s="32"/>
+      <c r="K48" s="32"/>
     </row>
   </sheetData>
-  <mergeCells count="71">
+  <mergeCells count="74">
     <mergeCell ref="F35:G35"/>
     <mergeCell ref="H33:I33"/>
     <mergeCell ref="H34:I34"/>
@@ -1833,12 +1850,10 @@
     <mergeCell ref="E12:E17"/>
     <mergeCell ref="E18:E23"/>
     <mergeCell ref="E24:E29"/>
-    <mergeCell ref="C12:D14"/>
-    <mergeCell ref="C15:D17"/>
-    <mergeCell ref="C18:D20"/>
-    <mergeCell ref="C21:D23"/>
-    <mergeCell ref="C24:D26"/>
-    <mergeCell ref="C27:D29"/>
+    <mergeCell ref="C14:D15"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="C20:D21"/>
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="F18:G23"/>
     <mergeCell ref="F24:G29"/>
@@ -1880,6 +1895,11 @@
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="C35:D35"/>
     <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C18:D19"/>
+    <mergeCell ref="C22:D23"/>
+    <mergeCell ref="C26:D27"/>
+    <mergeCell ref="C24:D25"/>
+    <mergeCell ref="C28:D29"/>
   </mergeCells>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.25" footer="0.25"/>
   <pageSetup paperSize="9" fitToWidth="0" orientation="portrait" r:id="rId1"/>

--- a/Template/Voucher Template.xlsx
+++ b/Template/Voucher Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Smart Travel PC\Desktop\Vouchers Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71887FCA-7627-42B4-B928-58DAA0508DAE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD0EB27-43F7-4366-BB11-C0960C4E1C7F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="19935" windowHeight="15525" xr2:uid="{46FCF62E-0F38-40EF-B40B-6239A54C7BFA}"/>
+    <workbookView xWindow="2340" yWindow="330" windowWidth="16650" windowHeight="15870" xr2:uid="{46FCF62E-0F38-40EF-B40B-6239A54C7BFA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="48">
   <si>
     <t>TO:</t>
   </si>
@@ -169,9 +169,6 @@
   </si>
   <si>
     <t>*** It will be subject to change based on the local situation ***</t>
-  </si>
-  <si>
-    <t>To</t>
   </si>
 </sst>
 </file>
@@ -443,7 +440,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -481,9 +478,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -491,40 +485,175 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -538,24 +667,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -581,137 +692,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -737,13 +728,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>19051</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>866775</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>695325</xdr:rowOff>
+      <xdr:rowOff>714375</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -772,7 +763,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19051" y="95250"/>
+          <a:off x="19051" y="114300"/>
           <a:ext cx="6638924" cy="600075"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1111,48 +1102,48 @@
       <c r="K1" s="2"/>
     </row>
     <row r="2" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="63"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="66"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="74"/>
       <c r="F2" s="13"/>
       <c r="G2" s="14"/>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="49"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="51"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="64"/>
       <c r="N2" s="2"/>
     </row>
     <row r="3" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="53"/>
-      <c r="K3" s="54"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="66"/>
       <c r="N3" s="2"/>
     </row>
     <row r="4" spans="1:14" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="16"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="A4" s="15"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
       <c r="G4" s="6"/>
-      <c r="H4" s="18"/>
+      <c r="H4" s="17"/>
       <c r="I4" s="5"/>
       <c r="J4" s="10"/>
       <c r="K4" s="9"/>
@@ -1162,64 +1153,64 @@
       <c r="A5" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="58" t="s">
+      <c r="B5" s="67" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="60" t="s">
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="61"/>
-      <c r="H5" s="55" t="s">
+      <c r="G5" s="70"/>
+      <c r="H5" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="56"/>
-      <c r="J5" s="56"/>
-      <c r="K5" s="57"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="64"/>
     </row>
     <row r="6" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="58" t="s">
+      <c r="B6" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="60" t="s">
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="61"/>
-      <c r="H6" s="55" t="s">
+      <c r="G6" s="70"/>
+      <c r="H6" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="56"/>
-      <c r="J6" s="56"/>
-      <c r="K6" s="57"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
     </row>
     <row r="7" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="59" t="s">
+      <c r="B7" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="60" t="s">
+      <c r="C7" s="68"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="61"/>
-      <c r="H7" s="55" t="s">
+      <c r="G7" s="70"/>
+      <c r="H7" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="I7" s="56"/>
-      <c r="J7" s="56"/>
-      <c r="K7" s="57"/>
+      <c r="I7" s="63"/>
+      <c r="J7" s="63"/>
+      <c r="K7" s="64"/>
     </row>
     <row r="8" spans="1:14" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
@@ -1235,19 +1226,19 @@
       <c r="K8" s="2"/>
     </row>
     <row r="9" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="30"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="30"/>
-      <c r="K9" s="30"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="24"/>
     </row>
     <row r="10" spans="1:14" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
@@ -1261,624 +1252,575 @@
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
+      <c r="M10" s="4"/>
     </row>
     <row r="11" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="52"/>
-      <c r="B11" s="77"/>
-      <c r="C11" s="74" t="s">
+      <c r="A11" s="35"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="76"/>
+      <c r="D11" s="44"/>
       <c r="E11" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="67" t="s">
+      <c r="F11" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="G11" s="67"/>
-      <c r="H11" s="74" t="s">
+      <c r="G11" s="52"/>
+      <c r="H11" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="I11" s="75"/>
-      <c r="J11" s="75"/>
-      <c r="K11" s="76"/>
+      <c r="I11" s="62"/>
+      <c r="J11" s="62"/>
+      <c r="K11" s="44"/>
+      <c r="M11" s="4"/>
     </row>
     <row r="12" spans="1:14" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="78"/>
-      <c r="B12" s="79"/>
-      <c r="C12" s="19">
+      <c r="A12" s="37"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="48">
         <v>45855</v>
       </c>
-      <c r="D12" s="20"/>
-      <c r="E12" s="84"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="37"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="36"/>
-      <c r="J12" s="36"/>
-      <c r="K12" s="37"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="53"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="54"/>
+      <c r="K12" s="55"/>
     </row>
     <row r="13" spans="1:14" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="80"/>
-      <c r="B13" s="81"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="85"/>
-      <c r="F13" s="68"/>
-      <c r="G13" s="69"/>
-      <c r="H13" s="68"/>
-      <c r="I13" s="72"/>
-      <c r="J13" s="72"/>
-      <c r="K13" s="69"/>
-    </row>
-    <row r="14" spans="1:14" s="4" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="80"/>
-      <c r="B14" s="81"/>
-      <c r="C14" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="24"/>
-      <c r="E14" s="85"/>
-      <c r="F14" s="68"/>
-      <c r="G14" s="69"/>
-      <c r="H14" s="70"/>
-      <c r="I14" s="73"/>
-      <c r="J14" s="73"/>
-      <c r="K14" s="71"/>
-    </row>
-    <row r="15" spans="1:14" s="4" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="80"/>
-      <c r="B15" s="81"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="85"/>
-      <c r="F15" s="68"/>
-      <c r="G15" s="69"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="36"/>
-      <c r="J15" s="36"/>
-      <c r="K15" s="37"/>
+      <c r="A13" s="39"/>
+      <c r="B13" s="40"/>
+      <c r="C13" s="50"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="57"/>
+      <c r="K13" s="58"/>
+    </row>
+    <row r="14" spans="1:14" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="39"/>
+      <c r="B14" s="40"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="59"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="60"/>
+      <c r="K14" s="61"/>
+    </row>
+    <row r="15" spans="1:14" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="39"/>
+      <c r="B15" s="40"/>
+      <c r="C15" s="87">
+        <v>45855</v>
+      </c>
+      <c r="D15" s="88"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="28"/>
     </row>
     <row r="16" spans="1:14" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="80"/>
-      <c r="B16" s="81"/>
-      <c r="C16" s="21">
+      <c r="A16" s="39"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="87"/>
+      <c r="D16" s="88"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="31"/>
+    </row>
+    <row r="17" spans="1:11" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="39"/>
+      <c r="B17" s="40"/>
+      <c r="C17" s="89"/>
+      <c r="D17" s="90"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="34"/>
+    </row>
+    <row r="18" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="39"/>
+      <c r="B18" s="40"/>
+      <c r="C18" s="48">
         <v>45855</v>
       </c>
-      <c r="D16" s="22"/>
-      <c r="E16" s="85"/>
-      <c r="F16" s="68"/>
-      <c r="G16" s="69"/>
-      <c r="H16" s="68"/>
-      <c r="I16" s="72"/>
-      <c r="J16" s="72"/>
-      <c r="K16" s="69"/>
-    </row>
-    <row r="17" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="80"/>
-      <c r="B17" s="81"/>
-      <c r="C17" s="87"/>
-      <c r="D17" s="88"/>
-      <c r="E17" s="86"/>
-      <c r="F17" s="70"/>
-      <c r="G17" s="71"/>
-      <c r="H17" s="70"/>
-      <c r="I17" s="73"/>
-      <c r="J17" s="73"/>
-      <c r="K17" s="71"/>
-    </row>
-    <row r="18" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="80"/>
-      <c r="B18" s="81"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="84"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="36"/>
-      <c r="J18" s="36"/>
-      <c r="K18" s="37"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="53"/>
+      <c r="I18" s="54"/>
+      <c r="J18" s="54"/>
+      <c r="K18" s="55"/>
     </row>
     <row r="19" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="80"/>
-      <c r="B19" s="81"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="85"/>
-      <c r="F19" s="68"/>
-      <c r="G19" s="69"/>
-      <c r="H19" s="68"/>
-      <c r="I19" s="72"/>
-      <c r="J19" s="72"/>
-      <c r="K19" s="69"/>
-    </row>
-    <row r="20" spans="1:11" s="4" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="80"/>
-      <c r="B20" s="81"/>
-      <c r="C20" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="D20" s="24"/>
-      <c r="E20" s="85"/>
-      <c r="F20" s="68"/>
-      <c r="G20" s="69"/>
-      <c r="H20" s="70"/>
-      <c r="I20" s="73"/>
-      <c r="J20" s="73"/>
-      <c r="K20" s="71"/>
-    </row>
-    <row r="21" spans="1:11" s="4" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="80"/>
-      <c r="B21" s="81"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="85"/>
-      <c r="F21" s="68"/>
-      <c r="G21" s="69"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="36"/>
-      <c r="J21" s="36"/>
-      <c r="K21" s="37"/>
+      <c r="A19" s="39"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="50"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="56"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="57"/>
+      <c r="K19" s="58"/>
+    </row>
+    <row r="20" spans="1:11" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="39"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="50"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="59"/>
+      <c r="I20" s="60"/>
+      <c r="J20" s="60"/>
+      <c r="K20" s="61"/>
+    </row>
+    <row r="21" spans="1:11" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="39"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="87">
+        <v>45855</v>
+      </c>
+      <c r="D21" s="88"/>
+      <c r="E21" s="46"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="27"/>
+      <c r="J21" s="27"/>
+      <c r="K21" s="28"/>
     </row>
     <row r="22" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="80"/>
-      <c r="B22" s="81"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="85"/>
-      <c r="F22" s="68"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="68"/>
-      <c r="I22" s="72"/>
-      <c r="J22" s="72"/>
-      <c r="K22" s="69"/>
-    </row>
-    <row r="23" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="80"/>
-      <c r="B23" s="81"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="86"/>
-      <c r="F23" s="70"/>
-      <c r="G23" s="71"/>
-      <c r="H23" s="70"/>
-      <c r="I23" s="73"/>
-      <c r="J23" s="73"/>
-      <c r="K23" s="71"/>
+      <c r="A22" s="39"/>
+      <c r="B22" s="40"/>
+      <c r="C22" s="87"/>
+      <c r="D22" s="88"/>
+      <c r="E22" s="46"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="29"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="31"/>
+    </row>
+    <row r="23" spans="1:11" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="39"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="89"/>
+      <c r="D23" s="90"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="33"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="34"/>
     </row>
     <row r="24" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="80"/>
-      <c r="B24" s="81"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="84"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="37"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="36"/>
-      <c r="J24" s="36"/>
-      <c r="K24" s="37"/>
+      <c r="A24" s="39"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="48">
+        <v>45855</v>
+      </c>
+      <c r="D24" s="49"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="53"/>
+      <c r="I24" s="54"/>
+      <c r="J24" s="54"/>
+      <c r="K24" s="55"/>
     </row>
     <row r="25" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="80"/>
-      <c r="B25" s="81"/>
-      <c r="C25" s="21"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="85"/>
-      <c r="F25" s="68"/>
-      <c r="G25" s="69"/>
-      <c r="H25" s="68"/>
-      <c r="I25" s="72"/>
-      <c r="J25" s="72"/>
-      <c r="K25" s="69"/>
-    </row>
-    <row r="26" spans="1:11" s="4" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="80"/>
-      <c r="B26" s="81"/>
-      <c r="C26" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="D26" s="24"/>
-      <c r="E26" s="85"/>
-      <c r="F26" s="68"/>
-      <c r="G26" s="69"/>
-      <c r="H26" s="70"/>
-      <c r="I26" s="73"/>
-      <c r="J26" s="73"/>
-      <c r="K26" s="71"/>
-    </row>
-    <row r="27" spans="1:11" s="4" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="80"/>
-      <c r="B27" s="81"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="85"/>
-      <c r="F27" s="68"/>
-      <c r="G27" s="69"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="36"/>
-      <c r="J27" s="36"/>
-      <c r="K27" s="37"/>
+      <c r="A25" s="39"/>
+      <c r="B25" s="40"/>
+      <c r="C25" s="50"/>
+      <c r="D25" s="51"/>
+      <c r="E25" s="46"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="56"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="57"/>
+      <c r="K25" s="58"/>
+    </row>
+    <row r="26" spans="1:11" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="39"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="50"/>
+      <c r="D26" s="51"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="60"/>
+      <c r="J26" s="60"/>
+      <c r="K26" s="61"/>
+    </row>
+    <row r="27" spans="1:11" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="39"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="87">
+        <v>45855</v>
+      </c>
+      <c r="D27" s="88"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="27"/>
+      <c r="J27" s="27"/>
+      <c r="K27" s="28"/>
     </row>
     <row r="28" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="80"/>
-      <c r="B28" s="81"/>
-      <c r="C28" s="23"/>
-      <c r="D28" s="24"/>
-      <c r="E28" s="85"/>
-      <c r="F28" s="68"/>
-      <c r="G28" s="69"/>
-      <c r="H28" s="68"/>
-      <c r="I28" s="72"/>
-      <c r="J28" s="72"/>
-      <c r="K28" s="69"/>
-    </row>
-    <row r="29" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="82"/>
-      <c r="B29" s="83"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="86"/>
-      <c r="F29" s="70"/>
-      <c r="G29" s="71"/>
-      <c r="H29" s="70"/>
-      <c r="I29" s="73"/>
-      <c r="J29" s="73"/>
-      <c r="K29" s="71"/>
-    </row>
-    <row r="30" spans="1:11" customFormat="1" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="A28" s="39"/>
+      <c r="B28" s="40"/>
+      <c r="C28" s="87"/>
+      <c r="D28" s="88"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="31"/>
+    </row>
+    <row r="29" spans="1:11" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="41"/>
+      <c r="B29" s="42"/>
+      <c r="C29" s="89"/>
+      <c r="D29" s="90"/>
+      <c r="E29" s="47"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="34"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="34"/>
+    </row>
+    <row r="30" spans="1:11" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="30" t="s">
+      <c r="A31" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="B31" s="33"/>
-      <c r="C31" s="34" t="s">
+      <c r="B31" s="77"/>
+      <c r="C31" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="D31" s="34"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="34"/>
-      <c r="G31" s="34"/>
-      <c r="H31" s="34"/>
-      <c r="I31" s="34"/>
-      <c r="J31" s="34"/>
-      <c r="K31" s="34"/>
+      <c r="D31" s="78"/>
+      <c r="E31" s="78"/>
+      <c r="F31" s="78"/>
+      <c r="G31" s="78"/>
+      <c r="H31" s="78"/>
+      <c r="I31" s="78"/>
+      <c r="J31" s="78"/>
+      <c r="K31" s="78"/>
     </row>
     <row r="32" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="33"/>
-      <c r="B32" s="33"/>
-      <c r="C32" s="34"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="34"/>
-      <c r="G32" s="34"/>
-      <c r="H32" s="34"/>
-      <c r="I32" s="34"/>
-      <c r="J32" s="34"/>
-      <c r="K32" s="34"/>
+      <c r="A32" s="77"/>
+      <c r="B32" s="77"/>
+      <c r="C32" s="78"/>
+      <c r="D32" s="78"/>
+      <c r="E32" s="78"/>
+      <c r="F32" s="78"/>
+      <c r="G32" s="78"/>
+      <c r="H32" s="78"/>
+      <c r="I32" s="78"/>
+      <c r="J32" s="78"/>
+      <c r="K32" s="78"/>
     </row>
     <row r="33" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="41" t="s">
+      <c r="A33" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="B33" s="42"/>
-      <c r="C33" s="33"/>
-      <c r="D33" s="33"/>
+      <c r="B33" s="80"/>
+      <c r="C33" s="77"/>
+      <c r="D33" s="77"/>
       <c r="E33" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F33" s="30" t="s">
+      <c r="F33" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="G33" s="30"/>
-      <c r="H33" s="92" t="s">
+      <c r="G33" s="24"/>
+      <c r="H33" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="I33" s="92"/>
-      <c r="J33" s="30" t="s">
+      <c r="I33" s="21"/>
+      <c r="J33" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="K33" s="30"/>
+      <c r="K33" s="24"/>
     </row>
     <row r="34" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="43"/>
-      <c r="B34" s="44"/>
-      <c r="C34" s="47" t="s">
+      <c r="A34" s="81"/>
+      <c r="B34" s="82"/>
+      <c r="C34" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="D34" s="48"/>
+      <c r="D34" s="86"/>
       <c r="E34" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="F34" s="57" t="s">
+      <c r="F34" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="G34" s="55"/>
-      <c r="H34" s="57" t="s">
+      <c r="G34" s="20"/>
+      <c r="H34" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="I34" s="55"/>
-      <c r="J34" s="57" t="s">
+      <c r="I34" s="20"/>
+      <c r="J34" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="K34" s="89"/>
+      <c r="K34" s="22"/>
     </row>
     <row r="35" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="45"/>
-      <c r="B35" s="46"/>
-      <c r="C35" s="47" t="s">
+      <c r="A35" s="83"/>
+      <c r="B35" s="84"/>
+      <c r="C35" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="D35" s="48"/>
+      <c r="D35" s="86"/>
       <c r="E35" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="F35" s="57" t="s">
+      <c r="F35" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="G35" s="55"/>
-      <c r="H35" s="57" t="s">
+      <c r="G35" s="20"/>
+      <c r="H35" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="I35" s="55"/>
-      <c r="J35" s="57" t="s">
+      <c r="I35" s="20"/>
+      <c r="J35" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="K35" s="89"/>
+      <c r="K35" s="22"/>
     </row>
     <row r="36" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="30" t="s">
+      <c r="A36" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="B36" s="33"/>
-      <c r="C36" s="30" t="s">
+      <c r="B36" s="77"/>
+      <c r="C36" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="D36" s="30"/>
-      <c r="E36" s="91" t="s">
+      <c r="D36" s="24"/>
+      <c r="E36" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="F36" s="91"/>
-      <c r="G36" s="30" t="s">
+      <c r="F36" s="25"/>
+      <c r="G36" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="H36" s="30"/>
-      <c r="I36" s="30"/>
-      <c r="J36" s="30"/>
-      <c r="K36" s="30"/>
+      <c r="H36" s="24"/>
+      <c r="I36" s="24"/>
+      <c r="J36" s="24"/>
+      <c r="K36" s="24"/>
     </row>
     <row r="37" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="33"/>
-      <c r="B37" s="33"/>
-      <c r="C37" s="89" t="s">
+      <c r="A37" s="77"/>
+      <c r="B37" s="77"/>
+      <c r="C37" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="D37" s="89"/>
-      <c r="E37" s="90">
+      <c r="D37" s="22"/>
+      <c r="E37" s="23">
         <v>0.99652777777777779</v>
       </c>
-      <c r="F37" s="90"/>
-      <c r="G37" s="89" t="s">
+      <c r="F37" s="23"/>
+      <c r="G37" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="H37" s="89"/>
-      <c r="I37" s="89"/>
-      <c r="J37" s="89"/>
-      <c r="K37" s="89"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="22"/>
+      <c r="K37" s="22"/>
     </row>
     <row r="38" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="33"/>
-      <c r="B38" s="33"/>
-      <c r="C38" s="89"/>
-      <c r="D38" s="89"/>
-      <c r="E38" s="90"/>
-      <c r="F38" s="90"/>
-      <c r="G38" s="89"/>
-      <c r="H38" s="89"/>
-      <c r="I38" s="89"/>
-      <c r="J38" s="89"/>
-      <c r="K38" s="89"/>
+      <c r="A38" s="77"/>
+      <c r="B38" s="77"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="23"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="22"/>
+      <c r="I38" s="22"/>
+      <c r="J38" s="22"/>
+      <c r="K38" s="22"/>
     </row>
     <row r="39" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="30" t="s">
+      <c r="A39" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="B39" s="30"/>
-      <c r="C39" s="35" t="s">
+      <c r="B39" s="24"/>
+      <c r="C39" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="D39" s="36"/>
-      <c r="E39" s="36"/>
-      <c r="F39" s="36"/>
-      <c r="G39" s="36"/>
-      <c r="H39" s="36"/>
-      <c r="I39" s="36"/>
-      <c r="J39" s="36"/>
-      <c r="K39" s="37"/>
+      <c r="D39" s="27"/>
+      <c r="E39" s="27"/>
+      <c r="F39" s="27"/>
+      <c r="G39" s="27"/>
+      <c r="H39" s="27"/>
+      <c r="I39" s="27"/>
+      <c r="J39" s="27"/>
+      <c r="K39" s="28"/>
     </row>
     <row r="40" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="30"/>
-      <c r="B40" s="30"/>
-      <c r="C40" s="68" t="s">
+      <c r="A40" s="24"/>
+      <c r="B40" s="24"/>
+      <c r="C40" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="D40" s="72"/>
-      <c r="E40" s="72"/>
-      <c r="F40" s="72"/>
-      <c r="G40" s="72"/>
-      <c r="H40" s="72"/>
-      <c r="I40" s="72"/>
-      <c r="J40" s="72"/>
-      <c r="K40" s="69"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="30"/>
+      <c r="K40" s="31"/>
     </row>
     <row r="41" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="30"/>
-      <c r="B41" s="30"/>
-      <c r="C41" s="68"/>
-      <c r="D41" s="72"/>
-      <c r="E41" s="72"/>
-      <c r="F41" s="72"/>
-      <c r="G41" s="72"/>
-      <c r="H41" s="72"/>
-      <c r="I41" s="72"/>
-      <c r="J41" s="72"/>
-      <c r="K41" s="69"/>
+      <c r="A41" s="24"/>
+      <c r="B41" s="24"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="30"/>
+      <c r="G41" s="30"/>
+      <c r="H41" s="30"/>
+      <c r="I41" s="30"/>
+      <c r="J41" s="30"/>
+      <c r="K41" s="31"/>
     </row>
     <row r="42" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="30"/>
-      <c r="B42" s="30"/>
-      <c r="C42" s="70"/>
-      <c r="D42" s="73"/>
-      <c r="E42" s="73"/>
-      <c r="F42" s="73"/>
-      <c r="G42" s="73"/>
-      <c r="H42" s="73"/>
-      <c r="I42" s="73"/>
-      <c r="J42" s="73"/>
-      <c r="K42" s="71"/>
+      <c r="A42" s="24"/>
+      <c r="B42" s="24"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="33"/>
+      <c r="E42" s="33"/>
+      <c r="F42" s="33"/>
+      <c r="G42" s="33"/>
+      <c r="H42" s="33"/>
+      <c r="I42" s="33"/>
+      <c r="J42" s="33"/>
+      <c r="K42" s="34"/>
     </row>
     <row r="43" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="30" t="s">
+      <c r="A43" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="B43" s="30"/>
-      <c r="C43" s="35" t="s">
+      <c r="B43" s="24"/>
+      <c r="C43" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="D43" s="36"/>
-      <c r="E43" s="36"/>
-      <c r="F43" s="36"/>
-      <c r="G43" s="36"/>
-      <c r="H43" s="36"/>
-      <c r="I43" s="36"/>
-      <c r="J43" s="36"/>
-      <c r="K43" s="37"/>
+      <c r="D43" s="27"/>
+      <c r="E43" s="27"/>
+      <c r="F43" s="27"/>
+      <c r="G43" s="27"/>
+      <c r="H43" s="27"/>
+      <c r="I43" s="27"/>
+      <c r="J43" s="27"/>
+      <c r="K43" s="28"/>
     </row>
     <row r="44" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="30"/>
-      <c r="B44" s="30"/>
-      <c r="C44" s="27"/>
-      <c r="D44" s="28"/>
-      <c r="E44" s="28"/>
-      <c r="F44" s="28"/>
-      <c r="G44" s="28"/>
-      <c r="H44" s="28"/>
-      <c r="I44" s="28"/>
-      <c r="J44" s="28"/>
-      <c r="K44" s="29"/>
+      <c r="A44" s="24"/>
+      <c r="B44" s="24"/>
+      <c r="C44" s="29"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="30"/>
+      <c r="G44" s="30"/>
+      <c r="H44" s="30"/>
+      <c r="I44" s="30"/>
+      <c r="J44" s="30"/>
+      <c r="K44" s="31"/>
     </row>
     <row r="45" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="30"/>
-      <c r="B45" s="30"/>
-      <c r="C45" s="27"/>
-      <c r="D45" s="28"/>
-      <c r="E45" s="28"/>
-      <c r="F45" s="28"/>
-      <c r="G45" s="28"/>
-      <c r="H45" s="28"/>
-      <c r="I45" s="28"/>
-      <c r="J45" s="28"/>
-      <c r="K45" s="29"/>
+      <c r="A45" s="24"/>
+      <c r="B45" s="24"/>
+      <c r="C45" s="29"/>
+      <c r="D45" s="30"/>
+      <c r="E45" s="30"/>
+      <c r="F45" s="30"/>
+      <c r="G45" s="30"/>
+      <c r="H45" s="30"/>
+      <c r="I45" s="30"/>
+      <c r="J45" s="30"/>
+      <c r="K45" s="31"/>
     </row>
     <row r="46" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="30"/>
-      <c r="B46" s="30"/>
-      <c r="C46" s="38"/>
-      <c r="D46" s="39"/>
-      <c r="E46" s="39"/>
-      <c r="F46" s="39"/>
-      <c r="G46" s="39"/>
-      <c r="H46" s="39"/>
-      <c r="I46" s="39"/>
-      <c r="J46" s="39"/>
-      <c r="K46" s="40"/>
+      <c r="A46" s="24"/>
+      <c r="B46" s="24"/>
+      <c r="C46" s="32"/>
+      <c r="D46" s="33"/>
+      <c r="E46" s="33"/>
+      <c r="F46" s="33"/>
+      <c r="G46" s="33"/>
+      <c r="H46" s="33"/>
+      <c r="I46" s="33"/>
+      <c r="J46" s="33"/>
+      <c r="K46" s="34"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A47" s="30" t="s">
+      <c r="A47" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="B47" s="30"/>
-      <c r="C47" s="31" t="s">
+      <c r="B47" s="24"/>
+      <c r="C47" s="75" t="s">
         <v>47</v>
       </c>
-      <c r="D47" s="32"/>
-      <c r="E47" s="32"/>
-      <c r="F47" s="32"/>
-      <c r="G47" s="32"/>
-      <c r="H47" s="32"/>
-      <c r="I47" s="32"/>
-      <c r="J47" s="32"/>
-      <c r="K47" s="32"/>
+      <c r="D47" s="76"/>
+      <c r="E47" s="76"/>
+      <c r="F47" s="76"/>
+      <c r="G47" s="76"/>
+      <c r="H47" s="76"/>
+      <c r="I47" s="76"/>
+      <c r="J47" s="76"/>
+      <c r="K47" s="76"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A48" s="30"/>
-      <c r="B48" s="30"/>
-      <c r="C48" s="32"/>
-      <c r="D48" s="32"/>
-      <c r="E48" s="32"/>
-      <c r="F48" s="32"/>
-      <c r="G48" s="32"/>
-      <c r="H48" s="32"/>
-      <c r="I48" s="32"/>
-      <c r="J48" s="32"/>
-      <c r="K48" s="32"/>
+      <c r="A48" s="24"/>
+      <c r="B48" s="24"/>
+      <c r="C48" s="76"/>
+      <c r="D48" s="76"/>
+      <c r="E48" s="76"/>
+      <c r="F48" s="76"/>
+      <c r="G48" s="76"/>
+      <c r="H48" s="76"/>
+      <c r="I48" s="76"/>
+      <c r="J48" s="76"/>
+      <c r="K48" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="74">
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="C37:D38"/>
-    <mergeCell ref="E37:F38"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="G36:K36"/>
-    <mergeCell ref="G37:K38"/>
-    <mergeCell ref="A39:B42"/>
-    <mergeCell ref="C39:K39"/>
-    <mergeCell ref="C40:K40"/>
-    <mergeCell ref="C41:K41"/>
-    <mergeCell ref="C42:K42"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B29"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E12:E17"/>
-    <mergeCell ref="E18:E23"/>
-    <mergeCell ref="E24:E29"/>
-    <mergeCell ref="C14:D15"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="C20:D21"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F18:G23"/>
-    <mergeCell ref="F24:G29"/>
-    <mergeCell ref="H12:K14"/>
-    <mergeCell ref="H15:K17"/>
-    <mergeCell ref="H18:K20"/>
-    <mergeCell ref="H21:K23"/>
-    <mergeCell ref="H24:K26"/>
-    <mergeCell ref="H27:K29"/>
-    <mergeCell ref="H11:K11"/>
-    <mergeCell ref="F12:G17"/>
-    <mergeCell ref="A9:K9"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="H5:K5"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:E2"/>
     <mergeCell ref="C45:K45"/>
     <mergeCell ref="A47:B48"/>
     <mergeCell ref="C47:K48"/>
@@ -1895,11 +1837,64 @@
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="C35:D35"/>
     <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C18:D19"/>
-    <mergeCell ref="C22:D23"/>
-    <mergeCell ref="C26:D27"/>
-    <mergeCell ref="C24:D25"/>
-    <mergeCell ref="C28:D29"/>
+    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="H5:K5"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F18:G23"/>
+    <mergeCell ref="F24:G29"/>
+    <mergeCell ref="H12:K14"/>
+    <mergeCell ref="H18:K20"/>
+    <mergeCell ref="H24:K26"/>
+    <mergeCell ref="H11:K11"/>
+    <mergeCell ref="F12:G17"/>
+    <mergeCell ref="H15:K16"/>
+    <mergeCell ref="H17:K17"/>
+    <mergeCell ref="H21:K22"/>
+    <mergeCell ref="H23:K23"/>
+    <mergeCell ref="H27:K28"/>
+    <mergeCell ref="H29:K29"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B29"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E12:E17"/>
+    <mergeCell ref="E18:E23"/>
+    <mergeCell ref="E24:E29"/>
+    <mergeCell ref="C12:D14"/>
+    <mergeCell ref="C15:D17"/>
+    <mergeCell ref="C18:D20"/>
+    <mergeCell ref="C21:D23"/>
+    <mergeCell ref="C24:D26"/>
+    <mergeCell ref="C27:D29"/>
+    <mergeCell ref="A39:B42"/>
+    <mergeCell ref="C39:K39"/>
+    <mergeCell ref="C40:K40"/>
+    <mergeCell ref="C41:K41"/>
+    <mergeCell ref="C42:K42"/>
+    <mergeCell ref="C37:D38"/>
+    <mergeCell ref="E37:F38"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="G36:K36"/>
+    <mergeCell ref="G37:K38"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="F34:G34"/>
   </mergeCells>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.25" footer="0.25"/>
   <pageSetup paperSize="9" fitToWidth="0" orientation="portrait" r:id="rId1"/>
